--- a/panchang-data/kashi2026.xlsx
+++ b/panchang-data/kashi2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dwivedi\Desktop\SiteDevelopment\Base Files To Make New Panchang Excel Files\Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jyotishiji.com\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66CD68F2-7C5D-448C-B474-EE0ACA1E20BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D257B2CE-6C5E-48B2-B772-98B3649E935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{E376EF16-9884-4357-862E-E45DA8BA8E62}"/>
+    <workbookView xWindow="13635" yWindow="2355" windowWidth="23850" windowHeight="11295" xr2:uid="{E376EF16-9884-4357-862E-E45DA8BA8E62}"/>
   </bookViews>
   <sheets>
     <sheet name="WORD_954" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5389">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16192,17 +16192,19 @@
   </si>
   <si>
     <t>121°05'07.11</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="00"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16219,6 +16221,16 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Nirmala UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Nirmala UI"/>
       <family val="2"/>
@@ -16241,32 +16253,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{26D8121C-151C-4065-8954-2CA324D0F04D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -16579,18 +16597,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA352D59-AF1F-4335-9DAD-3CA9941A63AD}">
   <dimension ref="A1:AB366"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="12.7109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" style="3" customWidth="1"/>
     <col min="5" max="19" width="16.7109375" style="4" customWidth="1"/>
     <col min="20" max="27" width="18.7109375" style="4" customWidth="1"/>
-    <col min="28" max="28" width="70.7109375" style="10" customWidth="1"/>
+    <col min="28" max="28" width="70.7109375" style="4" customWidth="1"/>
     <col min="29" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="8" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="8" customFormat="1" ht="21.95" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -16676,12 +16694,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="18" customHeight="1">
       <c r="A2" s="1">
         <v>46023</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
+      <c r="B2" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16758,16 +16776,16 @@
       <c r="AA2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB2" s="9" t="s">
+      <c r="AB2" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="18" customHeight="1">
       <c r="A3" s="1">
         <v>46024</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
+      <c r="B3" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16844,16 +16862,16 @@
       <c r="AA3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AB3" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="18" customHeight="1">
       <c r="A4" s="1">
         <v>46025</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
+      <c r="B4" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16930,16 +16948,16 @@
       <c r="AA4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AB4" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="18" customHeight="1">
       <c r="A5" s="1">
         <v>46026</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>88</v>
+      <c r="B5" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17016,16 +17034,16 @@
       <c r="AA5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AB5" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="18" customHeight="1">
       <c r="A6" s="1">
         <v>46027</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
+      <c r="B6" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17102,16 +17120,16 @@
       <c r="AA6" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AB6" s="9" t="s">
+      <c r="AB6" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="18" customHeight="1">
       <c r="A7" s="1">
         <v>46028</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>88</v>
+      <c r="B7" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17188,16 +17206,16 @@
       <c r="AA7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AB7" s="9" t="s">
+      <c r="AB7" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="18" customHeight="1">
       <c r="A8" s="1">
         <v>46029</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>88</v>
+      <c r="B8" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17274,16 +17292,16 @@
       <c r="AA8" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="AB8" s="9" t="s">
+      <c r="AB8" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="18" customHeight="1">
       <c r="A9" s="1">
         <v>46030</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>88</v>
+      <c r="B9" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17360,16 +17378,16 @@
       <c r="AA9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AB9" s="9" t="s">
+      <c r="AB9" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="18" customHeight="1">
       <c r="A10" s="1">
         <v>46031</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>88</v>
+      <c r="B10" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17446,16 +17464,16 @@
       <c r="AA10" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="AB10" s="9" t="s">
+      <c r="AB10" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="18" customHeight="1">
       <c r="A11" s="1">
         <v>46032</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17532,16 +17550,16 @@
       <c r="AA11" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AB11" s="9" t="s">
+      <c r="AB11" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="18" customHeight="1">
       <c r="A12" s="1">
         <v>46033</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>88</v>
+      <c r="B12" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17618,16 +17636,16 @@
       <c r="AA12" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="AB12" s="9" t="s">
+      <c r="AB12" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="18" customHeight="1">
       <c r="A13" s="1">
         <v>46034</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>88</v>
+      <c r="B13" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17704,16 +17722,16 @@
       <c r="AA13" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="AB13" s="9" t="s">
+      <c r="AB13" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="18" customHeight="1">
       <c r="A14" s="1">
         <v>46035</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>88</v>
+      <c r="B14" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17790,16 +17808,16 @@
       <c r="AA14" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AB14" s="9" t="s">
+      <c r="AB14" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="18" customHeight="1">
       <c r="A15" s="1">
         <v>46036</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>88</v>
+      <c r="B15" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17876,16 +17894,16 @@
       <c r="AA15" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AB15" s="9" t="s">
+      <c r="AB15" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="18" customHeight="1">
       <c r="A16" s="1">
         <v>46037</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>88</v>
+      <c r="B16" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17962,16 +17980,16 @@
       <c r="AA16" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AB16" s="9" t="s">
+      <c r="AB16" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="18" customHeight="1">
       <c r="A17" s="1">
         <v>46038</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>88</v>
+      <c r="B17" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18048,16 +18066,16 @@
       <c r="AA17" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AB17" s="9" t="s">
+      <c r="AB17" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="18" customHeight="1">
       <c r="A18" s="1">
         <v>46039</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>88</v>
+      <c r="B18" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18134,16 +18152,16 @@
       <c r="AA18" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="AB18" s="9" t="s">
+      <c r="AB18" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="18" customHeight="1">
       <c r="A19" s="1">
         <v>46040</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>88</v>
+      <c r="B19" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18220,16 +18238,16 @@
       <c r="AA19" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="AB19" s="9" t="s">
+      <c r="AB19" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="18" customHeight="1">
       <c r="A20" s="1">
         <v>46041</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>88</v>
+      <c r="B20" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18306,16 +18324,16 @@
       <c r="AA20" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="AB20" s="9" t="s">
+      <c r="AB20" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="18" customHeight="1">
       <c r="A21" s="1">
         <v>46042</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>88</v>
+      <c r="B21" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18392,16 +18410,16 @@
       <c r="AA21" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="AB21" s="9" t="s">
+      <c r="AB21" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="18" customHeight="1">
       <c r="A22" s="1">
         <v>46043</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>88</v>
+      <c r="B22" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18478,16 +18496,16 @@
       <c r="AA22" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="AB22" s="9" t="s">
+      <c r="AB22" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="18" customHeight="1">
       <c r="A23" s="1">
         <v>46044</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>88</v>
+      <c r="B23" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18564,16 +18582,16 @@
       <c r="AA23" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="AB23" s="9" t="s">
+      <c r="AB23" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="18" customHeight="1">
       <c r="A24" s="1">
         <v>46045</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>88</v>
+      <c r="B24" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18650,16 +18668,16 @@
       <c r="AA24" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AB24" s="9" t="s">
+      <c r="AB24" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="18" customHeight="1">
       <c r="A25" s="1">
         <v>46046</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>88</v>
+      <c r="B25" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18736,16 +18754,16 @@
       <c r="AA25" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="AB25" s="9" t="s">
+      <c r="AB25" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="18" customHeight="1">
       <c r="A26" s="1">
         <v>46047</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>88</v>
+      <c r="B26" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18822,16 +18840,16 @@
       <c r="AA26" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="AB26" s="9" t="s">
+      <c r="AB26" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="18" customHeight="1">
       <c r="A27" s="1">
         <v>46048</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>88</v>
+      <c r="B27" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18908,16 +18926,16 @@
       <c r="AA27" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="AB27" s="9" t="s">
+      <c r="AB27" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="18" customHeight="1">
       <c r="A28" s="1">
         <v>46049</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>88</v>
+      <c r="B28" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -18994,16 +19012,16 @@
       <c r="AA28" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AB28" s="9" t="s">
+      <c r="AB28" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="18" customHeight="1">
       <c r="A29" s="1">
         <v>46050</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>88</v>
+      <c r="B29" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19080,16 +19098,16 @@
       <c r="AA29" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="AB29" s="9" t="s">
+      <c r="AB29" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="18" customHeight="1">
       <c r="A30" s="1">
         <v>46051</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>88</v>
+      <c r="B30" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19166,16 +19184,16 @@
       <c r="AA30" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="AB30" s="9" t="s">
+      <c r="AB30" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="18" customHeight="1">
       <c r="A31" s="1">
         <v>46052</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>88</v>
+      <c r="B31" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19252,16 +19270,16 @@
       <c r="AA31" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="AB31" s="9" t="s">
+      <c r="AB31" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="18" customHeight="1">
       <c r="A32" s="1">
         <v>46053</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>88</v>
+      <c r="B32" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19338,16 +19356,16 @@
       <c r="AA32" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="AB32" s="9" t="s">
+      <c r="AB32" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="18" customHeight="1">
       <c r="A33" s="1">
         <v>46054</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>88</v>
+      <c r="B33" s="10" t="s">
+        <v>559</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19424,16 +19442,16 @@
       <c r="AA33" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="AB33" s="9" t="s">
+      <c r="AB33" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="18" customHeight="1">
       <c r="A34" s="1">
         <v>46055</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>559</v>
+      <c r="B34" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19510,16 +19528,16 @@
       <c r="AA34" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="AB34" s="9" t="s">
+      <c r="AB34" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="18" customHeight="1">
       <c r="A35" s="1">
         <v>46056</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>559</v>
+      <c r="B35" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19596,16 +19614,16 @@
       <c r="AA35" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="AB35" s="9" t="s">
+      <c r="AB35" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="18" customHeight="1">
       <c r="A36" s="1">
         <v>46057</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>559</v>
+      <c r="B36" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19682,16 +19700,16 @@
       <c r="AA36" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="AB36" s="9" t="s">
+      <c r="AB36" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="18" customHeight="1">
       <c r="A37" s="1">
         <v>46058</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>559</v>
+      <c r="B37" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19768,16 +19786,16 @@
       <c r="AA37" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="AB37" s="9" t="s">
+      <c r="AB37" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="18" customHeight="1">
       <c r="A38" s="1">
         <v>46059</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>559</v>
+      <c r="B38" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19854,16 +19872,16 @@
       <c r="AA38" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="AB38" s="9" t="s">
+      <c r="AB38" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="18" customHeight="1">
       <c r="A39" s="1">
         <v>46060</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>559</v>
+      <c r="B39" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19940,16 +19958,16 @@
       <c r="AA39" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="AB39" s="9" t="s">
+      <c r="AB39" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="18" customHeight="1">
       <c r="A40" s="1">
         <v>46061</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>559</v>
+      <c r="B40" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20026,16 +20044,16 @@
       <c r="AA40" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="AB40" s="9" t="s">
+      <c r="AB40" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="18" customHeight="1">
       <c r="A41" s="1">
         <v>46062</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>559</v>
+      <c r="B41" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20112,16 +20130,16 @@
       <c r="AA41" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="AB41" s="9" t="s">
+      <c r="AB41" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="18" customHeight="1">
       <c r="A42" s="1">
         <v>46063</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>559</v>
+      <c r="B42" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20198,16 +20216,16 @@
       <c r="AA42" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="AB42" s="9" t="s">
+      <c r="AB42" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="18" customHeight="1">
       <c r="A43" s="1">
         <v>46064</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>559</v>
+      <c r="B43" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20284,16 +20302,16 @@
       <c r="AA43" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="AB43" s="9" t="s">
+      <c r="AB43" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="18" customHeight="1">
       <c r="A44" s="1">
         <v>46065</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>559</v>
+      <c r="B44" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20370,16 +20388,16 @@
       <c r="AA44" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="AB44" s="9" t="s">
+      <c r="AB44" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="18" customHeight="1">
       <c r="A45" s="1">
         <v>46066</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>559</v>
+      <c r="B45" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20456,16 +20474,16 @@
       <c r="AA45" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="AB45" s="9" t="s">
+      <c r="AB45" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="18" customHeight="1">
       <c r="A46" s="1">
         <v>46067</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>559</v>
+      <c r="B46" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20542,16 +20560,16 @@
       <c r="AA46" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="AB46" s="9" t="s">
+      <c r="AB46" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="18" customHeight="1">
       <c r="A47" s="1">
         <v>46068</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>559</v>
+      <c r="B47" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20628,16 +20646,16 @@
       <c r="AA47" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="AB47" s="9" t="s">
+      <c r="AB47" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="18" customHeight="1">
       <c r="A48" s="1">
         <v>46069</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>559</v>
+      <c r="B48" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20714,16 +20732,16 @@
       <c r="AA48" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="AB48" s="9" t="s">
+      <c r="AB48" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" ht="18" customHeight="1">
       <c r="A49" s="1">
         <v>46070</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>559</v>
+      <c r="B49" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20800,16 +20818,16 @@
       <c r="AA49" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="AB49" s="9" t="s">
+      <c r="AB49" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="18" customHeight="1">
       <c r="A50" s="1">
         <v>46071</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>559</v>
+      <c r="B50" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20886,16 +20904,16 @@
       <c r="AA50" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="AB50" s="9" t="s">
+      <c r="AB50" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="18" customHeight="1">
       <c r="A51" s="1">
         <v>46072</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>559</v>
+      <c r="B51" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20972,16 +20990,16 @@
       <c r="AA51" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="AB51" s="9" t="s">
+      <c r="AB51" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="18" customHeight="1">
       <c r="A52" s="1">
         <v>46073</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>559</v>
+      <c r="B52" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21058,16 +21076,16 @@
       <c r="AA52" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="AB52" s="9" t="s">
+      <c r="AB52" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="18" customHeight="1">
       <c r="A53" s="1">
         <v>46074</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>559</v>
+      <c r="B53" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21144,16 +21162,16 @@
       <c r="AA53" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="AB53" s="9" t="s">
+      <c r="AB53" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="18" customHeight="1">
       <c r="A54" s="1">
         <v>46075</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>559</v>
+      <c r="B54" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21230,16 +21248,16 @@
       <c r="AA54" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="AB54" s="9" t="s">
+      <c r="AB54" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="18" customHeight="1">
       <c r="A55" s="1">
         <v>46076</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>559</v>
+      <c r="B55" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21316,16 +21334,16 @@
       <c r="AA55" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="AB55" s="9" t="s">
+      <c r="AB55" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="18" customHeight="1">
       <c r="A56" s="1">
         <v>46077</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>559</v>
+      <c r="B56" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21402,16 +21420,16 @@
       <c r="AA56" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="AB56" s="9" t="s">
+      <c r="AB56" s="2" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="18" customHeight="1">
       <c r="A57" s="1">
         <v>46078</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>559</v>
+      <c r="B57" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21488,16 +21506,16 @@
       <c r="AA57" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="AB57" s="9" t="s">
+      <c r="AB57" s="2" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="18" customHeight="1">
       <c r="A58" s="1">
         <v>46079</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>559</v>
+      <c r="B58" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21574,16 +21592,16 @@
       <c r="AA58" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="AB58" s="9" t="s">
+      <c r="AB58" s="2" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="18" customHeight="1">
       <c r="A59" s="1">
         <v>46080</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>559</v>
+      <c r="B59" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21660,16 +21678,16 @@
       <c r="AA59" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="AB59" s="9" t="s">
+      <c r="AB59" s="2" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="18" customHeight="1">
       <c r="A60" s="1">
         <v>46081</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>559</v>
+      <c r="B60" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21746,16 +21764,16 @@
       <c r="AA60" s="2" t="s">
         <v>953</v>
       </c>
-      <c r="AB60" s="9" t="s">
+      <c r="AB60" s="2" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="18" customHeight="1">
       <c r="A61" s="1">
         <v>46082</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>559</v>
+      <c r="B61" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21832,16 +21850,16 @@
       <c r="AA61" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="AB61" s="9" t="s">
+      <c r="AB61" s="2" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="18" customHeight="1">
       <c r="A62" s="1">
         <v>46083</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>559</v>
+      <c r="B62" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21918,16 +21936,16 @@
       <c r="AA62" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="AB62" s="9" t="s">
+      <c r="AB62" s="2" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="18" customHeight="1">
       <c r="A63" s="1">
         <v>46084</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>559</v>
+      <c r="B63" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22004,16 +22022,16 @@
       <c r="AA63" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="AB63" s="9" t="s">
+      <c r="AB63" s="2" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="18" customHeight="1">
       <c r="A64" s="1">
         <v>46085</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>999</v>
+      <c r="B64" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22090,16 +22108,16 @@
       <c r="AA64" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="AB64" s="9" t="s">
+      <c r="AB64" s="2" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" ht="18" customHeight="1">
       <c r="A65" s="1">
         <v>46086</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>999</v>
+      <c r="B65" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22176,16 +22194,16 @@
       <c r="AA65" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="AB65" s="9" t="s">
+      <c r="AB65" s="2" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" ht="18" customHeight="1">
       <c r="A66" s="1">
         <v>46087</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>999</v>
+      <c r="B66" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22262,16 +22280,16 @@
       <c r="AA66" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="AB66" s="9" t="s">
+      <c r="AB66" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="18" customHeight="1">
       <c r="A67" s="1">
         <v>46088</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>999</v>
+      <c r="B67" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22348,16 +22366,16 @@
       <c r="AA67" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="AB67" s="9" t="s">
+      <c r="AB67" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="18" customHeight="1">
       <c r="A68" s="1">
         <v>46089</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>999</v>
+      <c r="B68" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22434,16 +22452,16 @@
       <c r="AA68" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="AB68" s="9" t="s">
+      <c r="AB68" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="18" customHeight="1">
       <c r="A69" s="1">
         <v>46090</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>999</v>
+      <c r="B69" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22520,16 +22538,16 @@
       <c r="AA69" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="AB69" s="9" t="s">
+      <c r="AB69" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="18" customHeight="1">
       <c r="A70" s="1">
         <v>46091</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>999</v>
+      <c r="B70" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22606,16 +22624,16 @@
       <c r="AA70" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="AB70" s="9" t="s">
+      <c r="AB70" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" ht="18" customHeight="1">
       <c r="A71" s="1">
         <v>46092</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>999</v>
+      <c r="B71" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22692,16 +22710,16 @@
       <c r="AA71" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="AB71" s="9" t="s">
+      <c r="AB71" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="18" customHeight="1">
       <c r="A72" s="1">
         <v>46093</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>999</v>
+      <c r="B72" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22778,16 +22796,16 @@
       <c r="AA72" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="AB72" s="9" t="s">
+      <c r="AB72" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" ht="18" customHeight="1">
       <c r="A73" s="1">
         <v>46094</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>999</v>
+      <c r="B73" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22864,16 +22882,16 @@
       <c r="AA73" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="AB73" s="9" t="s">
+      <c r="AB73" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" ht="18" customHeight="1">
       <c r="A74" s="1">
         <v>46095</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>999</v>
+      <c r="B74" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22950,16 +22968,16 @@
       <c r="AA74" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="AB74" s="9" t="s">
+      <c r="AB74" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" ht="18" customHeight="1">
       <c r="A75" s="1">
         <v>46096</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>999</v>
+      <c r="B75" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23036,16 +23054,16 @@
       <c r="AA75" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="AB75" s="9" t="s">
+      <c r="AB75" s="2" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" ht="18" customHeight="1">
       <c r="A76" s="1">
         <v>46097</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>999</v>
+      <c r="B76" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23122,16 +23140,16 @@
       <c r="AA76" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="AB76" s="9" t="s">
+      <c r="AB76" s="2" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" ht="18" customHeight="1">
       <c r="A77" s="1">
         <v>46098</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>999</v>
+      <c r="B77" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23208,16 +23226,16 @@
       <c r="AA77" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="AB77" s="9" t="s">
+      <c r="AB77" s="2" t="s">
         <v>1204</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" ht="18" customHeight="1">
       <c r="A78" s="1">
         <v>46099</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>999</v>
+      <c r="B78" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23294,16 +23312,16 @@
       <c r="AA78" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="AB78" s="9" t="s">
+      <c r="AB78" s="2" t="s">
         <v>1204</v>
       </c>
     </row>
-    <row r="79" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" ht="18" customHeight="1">
       <c r="A79" s="1">
         <v>46100</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>999</v>
+      <c r="B79" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23380,16 +23398,16 @@
       <c r="AA79" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="AB79" s="9" t="s">
+      <c r="AB79" s="2" t="s">
         <v>1204</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" ht="18" customHeight="1">
       <c r="A80" s="1">
         <v>46101</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>999</v>
+      <c r="B80" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23466,16 +23484,16 @@
       <c r="AA80" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="AB80" s="9" t="s">
+      <c r="AB80" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="18" customHeight="1">
       <c r="A81" s="1">
         <v>46102</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>999</v>
+      <c r="B81" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23552,16 +23570,16 @@
       <c r="AA81" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="AB81" s="9" t="s">
+      <c r="AB81" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="18" customHeight="1">
       <c r="A82" s="1">
         <v>46103</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>999</v>
+      <c r="B82" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23638,16 +23656,16 @@
       <c r="AA82" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="AB82" s="9" t="s">
+      <c r="AB82" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="18" customHeight="1">
       <c r="A83" s="1">
         <v>46104</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>999</v>
+      <c r="B83" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23724,16 +23742,16 @@
       <c r="AA83" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="AB83" s="9" t="s">
+      <c r="AB83" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="18" customHeight="1">
       <c r="A84" s="1">
         <v>46105</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>999</v>
+      <c r="B84" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23810,16 +23828,16 @@
       <c r="AA84" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="AB84" s="9" t="s">
+      <c r="AB84" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="18" customHeight="1">
       <c r="A85" s="1">
         <v>46106</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>999</v>
+      <c r="B85" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23896,16 +23914,16 @@
       <c r="AA85" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="AB85" s="9" t="s">
+      <c r="AB85" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="18" customHeight="1">
       <c r="A86" s="1">
         <v>46107</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>999</v>
+      <c r="B86" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23982,16 +24000,16 @@
       <c r="AA86" s="2" t="s">
         <v>1338</v>
       </c>
-      <c r="AB86" s="9" t="s">
+      <c r="AB86" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="18" customHeight="1">
       <c r="A87" s="1">
         <v>46108</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>999</v>
+      <c r="B87" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24068,16 +24086,16 @@
       <c r="AA87" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="AB87" s="9" t="s">
+      <c r="AB87" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="18" customHeight="1">
       <c r="A88" s="1">
         <v>46109</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>999</v>
+      <c r="B88" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24154,16 +24172,16 @@
       <c r="AA88" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="AB88" s="9" t="s">
+      <c r="AB88" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="18" customHeight="1">
       <c r="A89" s="1">
         <v>46110</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>999</v>
+      <c r="B89" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24240,16 +24258,16 @@
       <c r="AA89" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="AB89" s="9" t="s">
+      <c r="AB89" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="18" customHeight="1">
       <c r="A90" s="1">
         <v>46111</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>999</v>
+      <c r="B90" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24326,16 +24344,16 @@
       <c r="AA90" s="2" t="s">
         <v>1395</v>
       </c>
-      <c r="AB90" s="9" t="s">
+      <c r="AB90" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="18" customHeight="1">
       <c r="A91" s="1">
         <v>46112</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>999</v>
+      <c r="B91" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24412,16 +24430,16 @@
       <c r="AA91" s="2" t="s">
         <v>1410</v>
       </c>
-      <c r="AB91" s="9" t="s">
+      <c r="AB91" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="18" customHeight="1">
       <c r="A92" s="1">
         <v>46113</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>999</v>
+      <c r="B92" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24498,16 +24516,16 @@
       <c r="AA92" s="2" t="s">
         <v>1424</v>
       </c>
-      <c r="AB92" s="9" t="s">
+      <c r="AB92" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="93" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" ht="18" customHeight="1">
       <c r="A93" s="1">
         <v>46114</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>999</v>
+      <c r="B93" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24584,16 +24602,16 @@
       <c r="AA93" s="2" t="s">
         <v>1439</v>
       </c>
-      <c r="AB93" s="9" t="s">
+      <c r="AB93" s="2" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="18" customHeight="1">
       <c r="A94" s="1">
         <v>46115</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>1440</v>
+      <c r="B94" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24670,16 +24688,16 @@
       <c r="AA94" s="2" t="s">
         <v>1454</v>
       </c>
-      <c r="AB94" s="9" t="s">
+      <c r="AB94" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="18" customHeight="1">
       <c r="A95" s="1">
         <v>46116</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>1440</v>
+      <c r="B95" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24756,16 +24774,16 @@
       <c r="AA95" s="2" t="s">
         <v>1469</v>
       </c>
-      <c r="AB95" s="9" t="s">
+      <c r="AB95" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="96" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="18" customHeight="1">
       <c r="A96" s="1">
         <v>46117</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>1440</v>
+      <c r="B96" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24842,16 +24860,16 @@
       <c r="AA96" s="2" t="s">
         <v>1484</v>
       </c>
-      <c r="AB96" s="9" t="s">
+      <c r="AB96" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="97" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="18" customHeight="1">
       <c r="A97" s="1">
         <v>46118</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>1440</v>
+      <c r="B97" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24928,16 +24946,16 @@
       <c r="AA97" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="AB97" s="9" t="s">
+      <c r="AB97" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="98" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="18" customHeight="1">
       <c r="A98" s="1">
         <v>46119</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>1440</v>
+      <c r="B98" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25014,16 +25032,16 @@
       <c r="AA98" s="2" t="s">
         <v>1512</v>
       </c>
-      <c r="AB98" s="9" t="s">
+      <c r="AB98" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="18" customHeight="1">
       <c r="A99" s="1">
         <v>46120</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>1440</v>
+      <c r="B99" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25100,16 +25118,16 @@
       <c r="AA99" s="2" t="s">
         <v>1526</v>
       </c>
-      <c r="AB99" s="9" t="s">
+      <c r="AB99" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="18" customHeight="1">
       <c r="A100" s="1">
         <v>46121</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>1440</v>
+      <c r="B100" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25186,16 +25204,16 @@
       <c r="AA100" s="2" t="s">
         <v>1540</v>
       </c>
-      <c r="AB100" s="9" t="s">
+      <c r="AB100" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="18" customHeight="1">
       <c r="A101" s="1">
         <v>46122</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>1440</v>
+      <c r="B101" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25272,16 +25290,16 @@
       <c r="AA101" s="2" t="s">
         <v>1555</v>
       </c>
-      <c r="AB101" s="9" t="s">
+      <c r="AB101" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="18" customHeight="1">
       <c r="A102" s="1">
         <v>46123</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>1440</v>
+      <c r="B102" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25358,16 +25376,16 @@
       <c r="AA102" s="2" t="s">
         <v>1569</v>
       </c>
-      <c r="AB102" s="9" t="s">
+      <c r="AB102" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="103" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="18" customHeight="1">
       <c r="A103" s="1">
         <v>46124</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>1440</v>
+      <c r="B103" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25444,16 +25462,16 @@
       <c r="AA103" s="2" t="s">
         <v>1585</v>
       </c>
-      <c r="AB103" s="9" t="s">
+      <c r="AB103" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="18" customHeight="1">
       <c r="A104" s="1">
         <v>46125</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>1440</v>
+      <c r="B104" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25530,16 +25548,16 @@
       <c r="AA104" s="2" t="s">
         <v>1599</v>
       </c>
-      <c r="AB104" s="9" t="s">
+      <c r="AB104" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="18" customHeight="1">
       <c r="A105" s="1">
         <v>46126</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>1440</v>
+      <c r="B105" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25616,16 +25634,16 @@
       <c r="AA105" s="2" t="s">
         <v>1613</v>
       </c>
-      <c r="AB105" s="9" t="s">
+      <c r="AB105" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="18" customHeight="1">
       <c r="A106" s="1">
         <v>46127</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>1440</v>
+      <c r="B106" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25702,16 +25720,16 @@
       <c r="AA106" s="2" t="s">
         <v>1628</v>
       </c>
-      <c r="AB106" s="9" t="s">
+      <c r="AB106" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="18" customHeight="1">
       <c r="A107" s="1">
         <v>46128</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>1440</v>
+      <c r="B107" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25788,16 +25806,16 @@
       <c r="AA107" s="2" t="s">
         <v>1642</v>
       </c>
-      <c r="AB107" s="9" t="s">
+      <c r="AB107" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="18" customHeight="1">
       <c r="A108" s="1">
         <v>46129</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>1440</v>
+      <c r="B108" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25874,16 +25892,16 @@
       <c r="AA108" s="2" t="s">
         <v>1657</v>
       </c>
-      <c r="AB108" s="9" t="s">
+      <c r="AB108" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="109" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="18" customHeight="1">
       <c r="A109" s="1">
         <v>46130</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>1440</v>
+      <c r="B109" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25960,16 +25978,16 @@
       <c r="AA109" s="2" t="s">
         <v>1671</v>
       </c>
-      <c r="AB109" s="9" t="s">
+      <c r="AB109" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="110" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="18" customHeight="1">
       <c r="A110" s="1">
         <v>46131</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>1440</v>
+      <c r="B110" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26046,16 +26064,16 @@
       <c r="AA110" s="2" t="s">
         <v>1686</v>
       </c>
-      <c r="AB110" s="9" t="s">
+      <c r="AB110" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="18" customHeight="1">
       <c r="A111" s="1">
         <v>46132</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>1440</v>
+      <c r="B111" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26132,16 +26150,16 @@
       <c r="AA111" s="2" t="s">
         <v>1700</v>
       </c>
-      <c r="AB111" s="9" t="s">
+      <c r="AB111" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="112" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" ht="18" customHeight="1">
       <c r="A112" s="1">
         <v>46133</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>1440</v>
+      <c r="B112" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26218,16 +26236,16 @@
       <c r="AA112" s="2" t="s">
         <v>1717</v>
       </c>
-      <c r="AB112" s="9" t="s">
+      <c r="AB112" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="18" customHeight="1">
       <c r="A113" s="1">
         <v>46134</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>1440</v>
+      <c r="B113" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26304,16 +26322,16 @@
       <c r="AA113" s="2" t="s">
         <v>1733</v>
       </c>
-      <c r="AB113" s="9" t="s">
+      <c r="AB113" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="18" customHeight="1">
       <c r="A114" s="1">
         <v>46135</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>1440</v>
+      <c r="B114" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26390,16 +26408,16 @@
       <c r="AA114" s="2" t="s">
         <v>1748</v>
       </c>
-      <c r="AB114" s="9" t="s">
+      <c r="AB114" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="18" customHeight="1">
       <c r="A115" s="1">
         <v>46136</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>1440</v>
+      <c r="B115" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26476,16 +26494,16 @@
       <c r="AA115" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="AB115" s="9" t="s">
+      <c r="AB115" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="18" customHeight="1">
       <c r="A116" s="1">
         <v>46137</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>1440</v>
+      <c r="B116" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26562,16 +26580,16 @@
       <c r="AA116" s="2" t="s">
         <v>1776</v>
       </c>
-      <c r="AB116" s="9" t="s">
+      <c r="AB116" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="18" customHeight="1">
       <c r="A117" s="1">
         <v>46138</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>1440</v>
+      <c r="B117" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26648,16 +26666,16 @@
       <c r="AA117" s="2" t="s">
         <v>1790</v>
       </c>
-      <c r="AB117" s="9" t="s">
+      <c r="AB117" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="18" customHeight="1">
       <c r="A118" s="1">
         <v>46139</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>1440</v>
+      <c r="B118" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26734,16 +26752,16 @@
       <c r="AA118" s="2" t="s">
         <v>1805</v>
       </c>
-      <c r="AB118" s="9" t="s">
+      <c r="AB118" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="18" customHeight="1">
       <c r="A119" s="1">
         <v>46140</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>1440</v>
+      <c r="B119" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26820,16 +26838,16 @@
       <c r="AA119" s="2" t="s">
         <v>1819</v>
       </c>
-      <c r="AB119" s="9" t="s">
+      <c r="AB119" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="18" customHeight="1">
       <c r="A120" s="1">
         <v>46141</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>1440</v>
+      <c r="B120" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26906,16 +26924,16 @@
       <c r="AA120" s="2" t="s">
         <v>1833</v>
       </c>
-      <c r="AB120" s="9" t="s">
+      <c r="AB120" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="18" customHeight="1">
       <c r="A121" s="1">
         <v>46142</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>1440</v>
+      <c r="B121" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26992,16 +27010,16 @@
       <c r="AA121" s="2" t="s">
         <v>1848</v>
       </c>
-      <c r="AB121" s="9" t="s">
+      <c r="AB121" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="18" customHeight="1">
       <c r="A122" s="1">
         <v>46143</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>1440</v>
+      <c r="B122" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27078,16 +27096,16 @@
       <c r="AA122" s="2" t="s">
         <v>1862</v>
       </c>
-      <c r="AB122" s="9" t="s">
+      <c r="AB122" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="123" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" ht="18" customHeight="1">
       <c r="A123" s="1">
         <v>46144</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>1863</v>
+      <c r="B123" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27164,16 +27182,16 @@
       <c r="AA123" s="2" t="s">
         <v>1878</v>
       </c>
-      <c r="AB123" s="9" t="s">
+      <c r="AB123" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="124" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" ht="18" customHeight="1">
       <c r="A124" s="1">
         <v>46145</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>1863</v>
+      <c r="B124" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27250,16 +27268,16 @@
       <c r="AA124" s="2" t="s">
         <v>1892</v>
       </c>
-      <c r="AB124" s="9" t="s">
+      <c r="AB124" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="125" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" ht="18" customHeight="1">
       <c r="A125" s="1">
         <v>46146</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>1863</v>
+      <c r="B125" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27336,16 +27354,16 @@
       <c r="AA125" s="2" t="s">
         <v>1906</v>
       </c>
-      <c r="AB125" s="9" t="s">
+      <c r="AB125" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="126" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" ht="18" customHeight="1">
       <c r="A126" s="1">
         <v>46147</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>1863</v>
+      <c r="B126" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27422,16 +27440,16 @@
       <c r="AA126" s="2" t="s">
         <v>1920</v>
       </c>
-      <c r="AB126" s="9" t="s">
+      <c r="AB126" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="127" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" ht="18" customHeight="1">
       <c r="A127" s="1">
         <v>46148</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>1863</v>
+      <c r="B127" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27508,16 +27526,16 @@
       <c r="AA127" s="2" t="s">
         <v>1934</v>
       </c>
-      <c r="AB127" s="9" t="s">
+      <c r="AB127" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="128" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" ht="18" customHeight="1">
       <c r="A128" s="1">
         <v>46149</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>1863</v>
+      <c r="B128" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27594,16 +27612,16 @@
       <c r="AA128" s="2" t="s">
         <v>1949</v>
       </c>
-      <c r="AB128" s="9" t="s">
+      <c r="AB128" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="129" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" ht="18" customHeight="1">
       <c r="A129" s="1">
         <v>46150</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>1863</v>
+      <c r="B129" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27680,16 +27698,16 @@
       <c r="AA129" s="2" t="s">
         <v>1962</v>
       </c>
-      <c r="AB129" s="9" t="s">
+      <c r="AB129" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="130" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:28" ht="18" customHeight="1">
       <c r="A130" s="1">
         <v>46151</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>1863</v>
+      <c r="B130" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27766,16 +27784,16 @@
       <c r="AA130" s="2" t="s">
         <v>1976</v>
       </c>
-      <c r="AB130" s="9" t="s">
+      <c r="AB130" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="131" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:28" ht="18" customHeight="1">
       <c r="A131" s="1">
         <v>46152</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>1863</v>
+      <c r="B131" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27852,16 +27870,16 @@
       <c r="AA131" s="2" t="s">
         <v>1991</v>
       </c>
-      <c r="AB131" s="9" t="s">
+      <c r="AB131" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="132" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:28" ht="18" customHeight="1">
       <c r="A132" s="1">
         <v>46153</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>1863</v>
+      <c r="B132" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27938,16 +27956,16 @@
       <c r="AA132" s="2" t="s">
         <v>2005</v>
       </c>
-      <c r="AB132" s="9" t="s">
+      <c r="AB132" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="133" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:28" ht="18" customHeight="1">
       <c r="A133" s="1">
         <v>46154</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>1863</v>
+      <c r="B133" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28024,16 +28042,16 @@
       <c r="AA133" s="2" t="s">
         <v>2020</v>
       </c>
-      <c r="AB133" s="9" t="s">
+      <c r="AB133" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="134" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:28" ht="18" customHeight="1">
       <c r="A134" s="1">
         <v>46155</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>1863</v>
+      <c r="B134" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28110,16 +28128,16 @@
       <c r="AA134" s="2" t="s">
         <v>2034</v>
       </c>
-      <c r="AB134" s="9" t="s">
+      <c r="AB134" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="135" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:28" ht="18" customHeight="1">
       <c r="A135" s="1">
         <v>46156</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>1863</v>
+      <c r="B135" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28196,16 +28214,16 @@
       <c r="AA135" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="AB135" s="9" t="s">
+      <c r="AB135" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="136" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:28" ht="18" customHeight="1">
       <c r="A136" s="1">
         <v>46157</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>1863</v>
+      <c r="B136" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28282,16 +28300,16 @@
       <c r="AA136" s="2" t="s">
         <v>2064</v>
       </c>
-      <c r="AB136" s="9" t="s">
+      <c r="AB136" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="137" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:28" ht="18" customHeight="1">
       <c r="A137" s="1">
         <v>46158</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>1863</v>
+      <c r="B137" s="10" t="s">
+        <v>2299</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28368,16 +28386,16 @@
       <c r="AA137" s="2" t="s">
         <v>2079</v>
       </c>
-      <c r="AB137" s="9" t="s">
+      <c r="AB137" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="138" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:28" ht="18" customHeight="1">
       <c r="A138" s="1">
         <v>46159</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>1863</v>
+      <c r="B138" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28454,16 +28472,16 @@
       <c r="AA138" s="2" t="s">
         <v>2094</v>
       </c>
-      <c r="AB138" s="9" t="s">
+      <c r="AB138" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="139" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:28" ht="18" customHeight="1">
       <c r="A139" s="1">
         <v>46160</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>1863</v>
+      <c r="B139" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28540,16 +28558,16 @@
       <c r="AA139" s="2" t="s">
         <v>2109</v>
       </c>
-      <c r="AB139" s="9" t="s">
+      <c r="AB139" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="140" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:28" ht="18" customHeight="1">
       <c r="A140" s="1">
         <v>46161</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>1863</v>
+      <c r="B140" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28626,16 +28644,16 @@
       <c r="AA140" s="2" t="s">
         <v>2123</v>
       </c>
-      <c r="AB140" s="9" t="s">
+      <c r="AB140" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="141" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:28" ht="18" customHeight="1">
       <c r="A141" s="1">
         <v>46162</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>1863</v>
+      <c r="B141" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28712,16 +28730,16 @@
       <c r="AA141" s="2" t="s">
         <v>2139</v>
       </c>
-      <c r="AB141" s="9" t="s">
+      <c r="AB141" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="142" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:28" ht="18" customHeight="1">
       <c r="A142" s="1">
         <v>46163</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>1863</v>
+      <c r="B142" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28798,16 +28816,16 @@
       <c r="AA142" s="2" t="s">
         <v>2153</v>
       </c>
-      <c r="AB142" s="9" t="s">
+      <c r="AB142" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="143" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:28" ht="18" customHeight="1">
       <c r="A143" s="1">
         <v>46164</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>1863</v>
+      <c r="B143" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28884,16 +28902,16 @@
       <c r="AA143" s="2" t="s">
         <v>2167</v>
       </c>
-      <c r="AB143" s="9" t="s">
+      <c r="AB143" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="144" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:28" ht="18" customHeight="1">
       <c r="A144" s="1">
         <v>46165</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>1863</v>
+      <c r="B144" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28970,16 +28988,16 @@
       <c r="AA144" s="2" t="s">
         <v>2181</v>
       </c>
-      <c r="AB144" s="9" t="s">
+      <c r="AB144" s="2" t="s">
         <v>2182</v>
       </c>
     </row>
-    <row r="145" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:28" ht="18" customHeight="1">
       <c r="A145" s="1">
         <v>46166</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>1863</v>
+      <c r="B145" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29056,16 +29074,16 @@
       <c r="AA145" s="2" t="s">
         <v>2196</v>
       </c>
-      <c r="AB145" s="9" t="s">
+      <c r="AB145" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="146" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:28" ht="18" customHeight="1">
       <c r="A146" s="1">
         <v>46167</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>1863</v>
+      <c r="B146" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29142,16 +29160,16 @@
       <c r="AA146" s="2" t="s">
         <v>2211</v>
       </c>
-      <c r="AB146" s="9" t="s">
+      <c r="AB146" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="147" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:28" ht="18" customHeight="1">
       <c r="A147" s="1">
         <v>46168</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>1863</v>
+      <c r="B147" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29228,16 +29246,16 @@
       <c r="AA147" s="2" t="s">
         <v>2225</v>
       </c>
-      <c r="AB147" s="9" t="s">
+      <c r="AB147" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="148" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:28" ht="18" customHeight="1">
       <c r="A148" s="1">
         <v>46169</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>1863</v>
+      <c r="B148" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29314,16 +29332,16 @@
       <c r="AA148" s="2" t="s">
         <v>2241</v>
       </c>
-      <c r="AB148" s="9" t="s">
+      <c r="AB148" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="149" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:28" ht="18" customHeight="1">
       <c r="A149" s="1">
         <v>46170</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>1863</v>
+      <c r="B149" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29400,16 +29418,16 @@
       <c r="AA149" s="2" t="s">
         <v>2255</v>
       </c>
-      <c r="AB149" s="9" t="s">
+      <c r="AB149" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="150" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:28" ht="18" customHeight="1">
       <c r="A150" s="1">
         <v>46171</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>1863</v>
+      <c r="B150" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29486,16 +29504,16 @@
       <c r="AA150" s="2" t="s">
         <v>2269</v>
       </c>
-      <c r="AB150" s="9" t="s">
+      <c r="AB150" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="151" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:28" ht="18" customHeight="1">
       <c r="A151" s="1">
         <v>46172</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>1863</v>
+      <c r="B151" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29572,16 +29590,16 @@
       <c r="AA151" s="2" t="s">
         <v>2284</v>
       </c>
-      <c r="AB151" s="9" t="s">
+      <c r="AB151" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="152" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:28" ht="18" customHeight="1">
       <c r="A152" s="1">
         <v>46173</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>1863</v>
+      <c r="B152" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29658,16 +29676,16 @@
       <c r="AA152" s="2" t="s">
         <v>2298</v>
       </c>
-      <c r="AB152" s="9" t="s">
+      <c r="AB152" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="153" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:28" ht="18" customHeight="1">
       <c r="A153" s="1">
         <v>46174</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>2299</v>
+      <c r="B153" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29744,16 +29762,16 @@
       <c r="AA153" s="2" t="s">
         <v>2313</v>
       </c>
-      <c r="AB153" s="9" t="s">
+      <c r="AB153" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="154" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:28" ht="18" customHeight="1">
       <c r="A154" s="1">
         <v>46175</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>2299</v>
+      <c r="B154" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29830,16 +29848,16 @@
       <c r="AA154" s="2" t="s">
         <v>2327</v>
       </c>
-      <c r="AB154" s="9" t="s">
+      <c r="AB154" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="155" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:28" ht="18" customHeight="1">
       <c r="A155" s="1">
         <v>46176</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>2299</v>
+      <c r="B155" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29916,16 +29934,16 @@
       <c r="AA155" s="2" t="s">
         <v>2341</v>
       </c>
-      <c r="AB155" s="9" t="s">
+      <c r="AB155" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="156" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:28" ht="18" customHeight="1">
       <c r="A156" s="1">
         <v>46177</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>2299</v>
+      <c r="B156" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30002,16 +30020,16 @@
       <c r="AA156" s="2" t="s">
         <v>2356</v>
       </c>
-      <c r="AB156" s="9" t="s">
+      <c r="AB156" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="157" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:28" ht="18" customHeight="1">
       <c r="A157" s="1">
         <v>46178</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>2299</v>
+      <c r="B157" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30088,16 +30106,16 @@
       <c r="AA157" s="2" t="s">
         <v>2369</v>
       </c>
-      <c r="AB157" s="9" t="s">
+      <c r="AB157" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="158" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:28" ht="18" customHeight="1">
       <c r="A158" s="1">
         <v>46179</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>2299</v>
+      <c r="B158" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30174,16 +30192,16 @@
       <c r="AA158" s="2" t="s">
         <v>2384</v>
       </c>
-      <c r="AB158" s="9" t="s">
+      <c r="AB158" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="159" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:28" ht="18" customHeight="1">
       <c r="A159" s="1">
         <v>46180</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>2299</v>
+      <c r="B159" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30260,16 +30278,16 @@
       <c r="AA159" s="2" t="s">
         <v>2398</v>
       </c>
-      <c r="AB159" s="9" t="s">
+      <c r="AB159" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="160" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:28" ht="18" customHeight="1">
       <c r="A160" s="1">
         <v>46181</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>2299</v>
+      <c r="B160" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30346,16 +30364,16 @@
       <c r="AA160" s="2" t="s">
         <v>2414</v>
       </c>
-      <c r="AB160" s="9" t="s">
+      <c r="AB160" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="161" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:28" ht="18" customHeight="1">
       <c r="A161" s="1">
         <v>46182</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>2299</v>
+      <c r="B161" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30432,16 +30450,16 @@
       <c r="AA161" s="2" t="s">
         <v>2428</v>
       </c>
-      <c r="AB161" s="9" t="s">
+      <c r="AB161" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="162" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:28" ht="18" customHeight="1">
       <c r="A162" s="1">
         <v>46183</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>2299</v>
+      <c r="B162" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30518,16 +30536,16 @@
       <c r="AA162" s="2" t="s">
         <v>2442</v>
       </c>
-      <c r="AB162" s="9" t="s">
+      <c r="AB162" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="163" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:28" ht="18" customHeight="1">
       <c r="A163" s="1">
         <v>46184</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>2299</v>
+      <c r="B163" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30604,16 +30622,16 @@
       <c r="AA163" s="2" t="s">
         <v>2456</v>
       </c>
-      <c r="AB163" s="9" t="s">
+      <c r="AB163" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="164" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:28" ht="18" customHeight="1">
       <c r="A164" s="1">
         <v>46185</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>2299</v>
+      <c r="B164" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30690,16 +30708,16 @@
       <c r="AA164" s="2" t="s">
         <v>2470</v>
       </c>
-      <c r="AB164" s="9" t="s">
+      <c r="AB164" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="165" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:28" ht="18" customHeight="1">
       <c r="A165" s="1">
         <v>46186</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>2299</v>
+      <c r="B165" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30776,16 +30794,16 @@
       <c r="AA165" s="2" t="s">
         <v>2484</v>
       </c>
-      <c r="AB165" s="9" t="s">
+      <c r="AB165" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="166" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:28" ht="18" customHeight="1">
       <c r="A166" s="1">
         <v>46187</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>2299</v>
+      <c r="B166" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30862,16 +30880,16 @@
       <c r="AA166" s="2" t="s">
         <v>2498</v>
       </c>
-      <c r="AB166" s="9" t="s">
+      <c r="AB166" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="167" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:28" ht="18" customHeight="1">
       <c r="A167" s="1">
         <v>46188</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>2299</v>
+      <c r="B167" s="10" t="s">
+        <v>5388</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
@@ -30948,15 +30966,15 @@
       <c r="AA167" s="2" t="s">
         <v>2513</v>
       </c>
-      <c r="AB167" s="9" t="s">
+      <c r="AB167" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="168" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:28" ht="18" customHeight="1">
       <c r="A168" s="1">
         <v>46189</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C168" s="2" t="s">
@@ -31034,15 +31052,15 @@
       <c r="AA168" s="2" t="s">
         <v>2529</v>
       </c>
-      <c r="AB168" s="9" t="s">
+      <c r="AB168" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="169" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:28" ht="18" customHeight="1">
       <c r="A169" s="1">
         <v>46190</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C169" s="2" t="s">
@@ -31120,15 +31138,15 @@
       <c r="AA169" s="2" t="s">
         <v>2544</v>
       </c>
-      <c r="AB169" s="9" t="s">
+      <c r="AB169" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="170" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:28" ht="18" customHeight="1">
       <c r="A170" s="1">
         <v>46191</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -31206,15 +31224,15 @@
       <c r="AA170" s="2" t="s">
         <v>2558</v>
       </c>
-      <c r="AB170" s="9" t="s">
+      <c r="AB170" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="171" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:28" ht="18" customHeight="1">
       <c r="A171" s="1">
         <v>46192</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C171" s="2" t="s">
@@ -31292,15 +31310,15 @@
       <c r="AA171" s="2" t="s">
         <v>2572</v>
       </c>
-      <c r="AB171" s="9" t="s">
+      <c r="AB171" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="172" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:28" ht="18" customHeight="1">
       <c r="A172" s="1">
         <v>46193</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -31378,15 +31396,15 @@
       <c r="AA172" s="2" t="s">
         <v>2586</v>
       </c>
-      <c r="AB172" s="9" t="s">
+      <c r="AB172" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="173" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:28" ht="18" customHeight="1">
       <c r="A173" s="1">
         <v>46194</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="B173" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C173" s="2" t="s">
@@ -31464,15 +31482,15 @@
       <c r="AA173" s="2" t="s">
         <v>2601</v>
       </c>
-      <c r="AB173" s="9" t="s">
+      <c r="AB173" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="174" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:28" ht="18" customHeight="1">
       <c r="A174" s="1">
         <v>46195</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B174" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C174" s="2" t="s">
@@ -31550,15 +31568,15 @@
       <c r="AA174" s="2" t="s">
         <v>2615</v>
       </c>
-      <c r="AB174" s="9" t="s">
+      <c r="AB174" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="175" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:28" ht="18" customHeight="1">
       <c r="A175" s="1">
         <v>46196</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B175" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -31636,15 +31654,15 @@
       <c r="AA175" s="2" t="s">
         <v>2630</v>
       </c>
-      <c r="AB175" s="9" t="s">
+      <c r="AB175" s="2" t="s">
         <v>2631</v>
       </c>
     </row>
-    <row r="176" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:28" ht="18" customHeight="1">
       <c r="A176" s="1">
         <v>46197</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B176" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C176" s="2" t="s">
@@ -31722,15 +31740,15 @@
       <c r="AA176" s="2" t="s">
         <v>2645</v>
       </c>
-      <c r="AB176" s="9" t="s">
+      <c r="AB176" s="2" t="s">
         <v>2631</v>
       </c>
     </row>
-    <row r="177" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:28" ht="18" customHeight="1">
       <c r="A177" s="1">
         <v>46198</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B177" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -31808,15 +31826,15 @@
       <c r="AA177" s="2" t="s">
         <v>2659</v>
       </c>
-      <c r="AB177" s="9" t="s">
+      <c r="AB177" s="2" t="s">
         <v>2631</v>
       </c>
     </row>
-    <row r="178" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:28" ht="18" customHeight="1">
       <c r="A178" s="1">
         <v>46199</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B178" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C178" s="2" t="s">
@@ -31894,15 +31912,15 @@
       <c r="AA178" s="2" t="s">
         <v>2673</v>
       </c>
-      <c r="AB178" s="9" t="s">
+      <c r="AB178" s="2" t="s">
         <v>2631</v>
       </c>
     </row>
-    <row r="179" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:28" ht="18" customHeight="1">
       <c r="A179" s="1">
         <v>46200</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B179" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C179" s="2" t="s">
@@ -31980,15 +31998,15 @@
       <c r="AA179" s="2" t="s">
         <v>2687</v>
       </c>
-      <c r="AB179" s="9" t="s">
+      <c r="AB179" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="180" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:28" ht="18" customHeight="1">
       <c r="A180" s="1">
         <v>46201</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C180" s="2" t="s">
@@ -32066,15 +32084,15 @@
       <c r="AA180" s="2" t="s">
         <v>2702</v>
       </c>
-      <c r="AB180" s="9" t="s">
+      <c r="AB180" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="181" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:28" ht="18" customHeight="1">
       <c r="A181" s="1">
         <v>46202</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" s="10" t="s">
         <v>2299</v>
       </c>
       <c r="C181" s="2" t="s">
@@ -32152,15 +32170,15 @@
       <c r="AA181" s="2" t="s">
         <v>2716</v>
       </c>
-      <c r="AB181" s="9" t="s">
+      <c r="AB181" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="182" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:28" ht="18" customHeight="1">
       <c r="A182" s="1">
         <v>46203</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B182" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -32238,15 +32256,15 @@
       <c r="AA182" s="2" t="s">
         <v>2731</v>
       </c>
-      <c r="AB182" s="9" t="s">
+      <c r="AB182" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="183" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:28" ht="18" customHeight="1">
       <c r="A183" s="1">
         <v>46204</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C183" s="2" t="s">
@@ -32324,15 +32342,15 @@
       <c r="AA183" s="2" t="s">
         <v>2746</v>
       </c>
-      <c r="AB183" s="9" t="s">
+      <c r="AB183" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="184" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:28" ht="18" customHeight="1">
       <c r="A184" s="1">
         <v>46205</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B184" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C184" s="2" t="s">
@@ -32410,15 +32428,15 @@
       <c r="AA184" s="2" t="s">
         <v>2760</v>
       </c>
-      <c r="AB184" s="9" t="s">
+      <c r="AB184" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="185" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:28" ht="18" customHeight="1">
       <c r="A185" s="1">
         <v>46206</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B185" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C185" s="2" t="s">
@@ -32496,15 +32514,15 @@
       <c r="AA185" s="2" t="s">
         <v>2775</v>
       </c>
-      <c r="AB185" s="9" t="s">
+      <c r="AB185" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="186" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:28" ht="18" customHeight="1">
       <c r="A186" s="1">
         <v>46207</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B186" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C186" s="2" t="s">
@@ -32582,15 +32600,15 @@
       <c r="AA186" s="2" t="s">
         <v>2789</v>
       </c>
-      <c r="AB186" s="9" t="s">
+      <c r="AB186" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="187" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:28" ht="18" customHeight="1">
       <c r="A187" s="1">
         <v>46208</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C187" s="2" t="s">
@@ -32668,15 +32686,15 @@
       <c r="AA187" s="2" t="s">
         <v>2802</v>
       </c>
-      <c r="AB187" s="9" t="s">
+      <c r="AB187" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="188" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:28" ht="18" customHeight="1">
       <c r="A188" s="1">
         <v>46209</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B188" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C188" s="2" t="s">
@@ -32754,15 +32772,15 @@
       <c r="AA188" s="2" t="s">
         <v>2816</v>
       </c>
-      <c r="AB188" s="9" t="s">
+      <c r="AB188" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="189" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:28" ht="18" customHeight="1">
       <c r="A189" s="1">
         <v>46210</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C189" s="2" t="s">
@@ -32840,15 +32858,15 @@
       <c r="AA189" s="2" t="s">
         <v>2829</v>
       </c>
-      <c r="AB189" s="9" t="s">
+      <c r="AB189" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="190" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:28" ht="18" customHeight="1">
       <c r="A190" s="1">
         <v>46211</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C190" s="2" t="s">
@@ -32926,15 +32944,15 @@
       <c r="AA190" s="2" t="s">
         <v>2842</v>
       </c>
-      <c r="AB190" s="9" t="s">
+      <c r="AB190" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="191" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:28" ht="18" customHeight="1">
       <c r="A191" s="1">
         <v>46212</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B191" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C191" s="2" t="s">
@@ -33012,15 +33030,15 @@
       <c r="AA191" s="2" t="s">
         <v>2859</v>
       </c>
-      <c r="AB191" s="9" t="s">
+      <c r="AB191" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="192" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:28" ht="18" customHeight="1">
       <c r="A192" s="1">
         <v>46213</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B192" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C192" s="2" t="s">
@@ -33098,15 +33116,15 @@
       <c r="AA192" s="2" t="s">
         <v>2873</v>
       </c>
-      <c r="AB192" s="9" t="s">
+      <c r="AB192" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="193" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:28" ht="18" customHeight="1">
       <c r="A193" s="1">
         <v>46214</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C193" s="2" t="s">
@@ -33184,15 +33202,15 @@
       <c r="AA193" s="2" t="s">
         <v>2886</v>
       </c>
-      <c r="AB193" s="9" t="s">
+      <c r="AB193" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="194" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:28" ht="18" customHeight="1">
       <c r="A194" s="1">
         <v>46215</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C194" s="2" t="s">
@@ -33270,15 +33288,15 @@
       <c r="AA194" s="2" t="s">
         <v>2902</v>
       </c>
-      <c r="AB194" s="9" t="s">
+      <c r="AB194" s="2" t="s">
         <v>2688</v>
       </c>
     </row>
-    <row r="195" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:28" ht="18" customHeight="1">
       <c r="A195" s="1">
         <v>46216</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B195" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -33356,15 +33374,15 @@
       <c r="AA195" s="2" t="s">
         <v>2917</v>
       </c>
-      <c r="AB195" s="9" t="s">
+      <c r="AB195" s="2" t="s">
         <v>2631</v>
       </c>
     </row>
-    <row r="196" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:28" ht="18" customHeight="1">
       <c r="A196" s="1">
         <v>46217</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="B196" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -33442,15 +33460,15 @@
       <c r="AA196" s="2" t="s">
         <v>2932</v>
       </c>
-      <c r="AB196" s="9" t="s">
+      <c r="AB196" s="2" t="s">
         <v>2933</v>
       </c>
     </row>
-    <row r="197" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:28" ht="18" customHeight="1">
       <c r="A197" s="1">
         <v>46218</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="B197" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C197" s="2" t="s">
@@ -33528,15 +33546,15 @@
       <c r="AA197" s="2" t="s">
         <v>2947</v>
       </c>
-      <c r="AB197" s="9" t="s">
+      <c r="AB197" s="2" t="s">
         <v>2933</v>
       </c>
     </row>
-    <row r="198" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:28" ht="18" customHeight="1">
       <c r="A198" s="1">
         <v>46219</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C198" s="2" t="s">
@@ -33614,15 +33632,15 @@
       <c r="AA198" s="2" t="s">
         <v>2961</v>
       </c>
-      <c r="AB198" s="9" t="s">
+      <c r="AB198" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="199" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:28" ht="18" customHeight="1">
       <c r="A199" s="1">
         <v>46220</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C199" s="2" t="s">
@@ -33700,15 +33718,15 @@
       <c r="AA199" s="2" t="s">
         <v>2977</v>
       </c>
-      <c r="AB199" s="9" t="s">
+      <c r="AB199" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="200" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:28" ht="18" customHeight="1">
       <c r="A200" s="1">
         <v>46221</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B200" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -33786,15 +33804,15 @@
       <c r="AA200" s="2" t="s">
         <v>2992</v>
       </c>
-      <c r="AB200" s="9" t="s">
+      <c r="AB200" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="201" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:28" ht="18" customHeight="1">
       <c r="A201" s="1">
         <v>46222</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B201" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C201" s="2" t="s">
@@ -33872,15 +33890,15 @@
       <c r="AA201" s="2" t="s">
         <v>3006</v>
       </c>
-      <c r="AB201" s="9" t="s">
+      <c r="AB201" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="202" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:28" ht="18" customHeight="1">
       <c r="A202" s="1">
         <v>46223</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B202" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C202" s="2" t="s">
@@ -33958,15 +33976,15 @@
       <c r="AA202" s="2" t="s">
         <v>3020</v>
       </c>
-      <c r="AB202" s="9" t="s">
+      <c r="AB202" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="203" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:28" ht="18" customHeight="1">
       <c r="A203" s="1">
         <v>46224</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -34044,15 +34062,15 @@
       <c r="AA203" s="2" t="s">
         <v>3035</v>
       </c>
-      <c r="AB203" s="9" t="s">
+      <c r="AB203" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="204" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:28" ht="18" customHeight="1">
       <c r="A204" s="1">
         <v>46225</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="B204" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C204" s="2" t="s">
@@ -34130,15 +34148,15 @@
       <c r="AA204" s="2" t="s">
         <v>3048</v>
       </c>
-      <c r="AB204" s="9" t="s">
+      <c r="AB204" s="2" t="s">
         <v>2962</v>
       </c>
     </row>
-    <row r="205" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:28" ht="18" customHeight="1">
       <c r="A205" s="1">
         <v>46226</v>
       </c>
-      <c r="B205" s="2" t="s">
+      <c r="B205" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C205" s="2" t="s">
@@ -34216,15 +34234,15 @@
       <c r="AA205" s="2" t="s">
         <v>3063</v>
       </c>
-      <c r="AB205" s="9" t="s">
+      <c r="AB205" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="206" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:28" ht="18" customHeight="1">
       <c r="A206" s="1">
         <v>46227</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="B206" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C206" s="2" t="s">
@@ -34302,15 +34320,15 @@
       <c r="AA206" s="2" t="s">
         <v>3078</v>
       </c>
-      <c r="AB206" s="9" t="s">
+      <c r="AB206" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="207" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:28" ht="18" customHeight="1">
       <c r="A207" s="1">
         <v>46228</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="B207" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C207" s="2" t="s">
@@ -34388,15 +34406,15 @@
       <c r="AA207" s="2" t="s">
         <v>3092</v>
       </c>
-      <c r="AB207" s="9" t="s">
+      <c r="AB207" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="208" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:28" ht="18" customHeight="1">
       <c r="A208" s="1">
         <v>46229</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C208" s="2" t="s">
@@ -34474,15 +34492,15 @@
       <c r="AA208" s="2" t="s">
         <v>3106</v>
       </c>
-      <c r="AB208" s="9" t="s">
+      <c r="AB208" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="209" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:28" ht="18" customHeight="1">
       <c r="A209" s="1">
         <v>46230</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C209" s="2" t="s">
@@ -34560,15 +34578,15 @@
       <c r="AA209" s="2" t="s">
         <v>3120</v>
       </c>
-      <c r="AB209" s="9" t="s">
+      <c r="AB209" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="210" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:28" ht="18" customHeight="1">
       <c r="A210" s="1">
         <v>46231</v>
       </c>
-      <c r="B210" s="2" t="s">
+      <c r="B210" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -34646,15 +34664,15 @@
       <c r="AA210" s="2" t="s">
         <v>3134</v>
       </c>
-      <c r="AB210" s="9" t="s">
+      <c r="AB210" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="211" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:28" ht="18" customHeight="1">
       <c r="A211" s="1">
         <v>46232</v>
       </c>
-      <c r="B211" s="2" t="s">
+      <c r="B211" s="9" t="s">
         <v>2717</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -34732,15 +34750,15 @@
       <c r="AA211" s="2" t="s">
         <v>3148</v>
       </c>
-      <c r="AB211" s="9" t="s">
+      <c r="AB211" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="212" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:28" ht="18" customHeight="1">
       <c r="A212" s="1">
         <v>46233</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B212" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -34818,15 +34836,15 @@
       <c r="AA212" s="2" t="s">
         <v>3163</v>
       </c>
-      <c r="AB212" s="9" t="s">
+      <c r="AB212" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="213" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:28" ht="18" customHeight="1">
       <c r="A213" s="1">
         <v>46234</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B213" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C213" s="2" t="s">
@@ -34904,15 +34922,15 @@
       <c r="AA213" s="2" t="s">
         <v>3178</v>
       </c>
-      <c r="AB213" s="9" t="s">
+      <c r="AB213" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="214" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:28" ht="18" customHeight="1">
       <c r="A214" s="1">
         <v>46235</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B214" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -34990,15 +35008,15 @@
       <c r="AA214" s="2" t="s">
         <v>3191</v>
       </c>
-      <c r="AB214" s="9" t="s">
+      <c r="AB214" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="215" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:28" ht="18" customHeight="1">
       <c r="A215" s="1">
         <v>46236</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B215" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -35076,15 +35094,15 @@
       <c r="AA215" s="2" t="s">
         <v>3206</v>
       </c>
-      <c r="AB215" s="9" t="s">
+      <c r="AB215" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="216" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:28" ht="18" customHeight="1">
       <c r="A216" s="1">
         <v>46237</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="B216" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C216" s="2" t="s">
@@ -35162,15 +35180,15 @@
       <c r="AA216" s="2" t="s">
         <v>3220</v>
       </c>
-      <c r="AB216" s="9" t="s">
+      <c r="AB216" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="217" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:28" ht="18" customHeight="1">
       <c r="A217" s="1">
         <v>46238</v>
       </c>
-      <c r="B217" s="2" t="s">
+      <c r="B217" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C217" s="2" t="s">
@@ -35248,15 +35266,15 @@
       <c r="AA217" s="2" t="s">
         <v>3234</v>
       </c>
-      <c r="AB217" s="9" t="s">
+      <c r="AB217" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="218" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:28" ht="18" customHeight="1">
       <c r="A218" s="1">
         <v>46239</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C218" s="2" t="s">
@@ -35334,15 +35352,15 @@
       <c r="AA218" s="2" t="s">
         <v>3249</v>
       </c>
-      <c r="AB218" s="9" t="s">
+      <c r="AB218" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="219" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:28" ht="18" customHeight="1">
       <c r="A219" s="1">
         <v>46240</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -35420,15 +35438,15 @@
       <c r="AA219" s="2" t="s">
         <v>3264</v>
       </c>
-      <c r="AB219" s="9" t="s">
+      <c r="AB219" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="220" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:28" ht="18" customHeight="1">
       <c r="A220" s="1">
         <v>46241</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C220" s="2" t="s">
@@ -35506,15 +35524,15 @@
       <c r="AA220" s="2" t="s">
         <v>3278</v>
       </c>
-      <c r="AB220" s="9" t="s">
+      <c r="AB220" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="221" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:28" ht="18" customHeight="1">
       <c r="A221" s="1">
         <v>46242</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C221" s="2" t="s">
@@ -35592,15 +35610,15 @@
       <c r="AA221" s="2" t="s">
         <v>3294</v>
       </c>
-      <c r="AB221" s="9" t="s">
+      <c r="AB221" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="222" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:28" ht="18" customHeight="1">
       <c r="A222" s="1">
         <v>46243</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -35678,15 +35696,15 @@
       <c r="AA222" s="2" t="s">
         <v>3308</v>
       </c>
-      <c r="AB222" s="9" t="s">
+      <c r="AB222" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="223" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:28" ht="18" customHeight="1">
       <c r="A223" s="1">
         <v>46244</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C223" s="2" t="s">
@@ -35764,15 +35782,15 @@
       <c r="AA223" s="2" t="s">
         <v>3324</v>
       </c>
-      <c r="AB223" s="9" t="s">
+      <c r="AB223" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="224" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:28" ht="18" customHeight="1">
       <c r="A224" s="1">
         <v>46245</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C224" s="2" t="s">
@@ -35850,15 +35868,15 @@
       <c r="AA224" s="2" t="s">
         <v>3338</v>
       </c>
-      <c r="AB224" s="9" t="s">
+      <c r="AB224" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="225" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:28" ht="18" customHeight="1">
       <c r="A225" s="1">
         <v>46246</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C225" s="2" t="s">
@@ -35936,15 +35954,15 @@
       <c r="AA225" s="2" t="s">
         <v>3352</v>
       </c>
-      <c r="AB225" s="9" t="s">
+      <c r="AB225" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="226" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:28" ht="18" customHeight="1">
       <c r="A226" s="1">
         <v>46247</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C226" s="2" t="s">
@@ -36022,15 +36040,15 @@
       <c r="AA226" s="2" t="s">
         <v>3366</v>
       </c>
-      <c r="AB226" s="9" t="s">
+      <c r="AB226" s="2" t="s">
         <v>3064</v>
       </c>
     </row>
-    <row r="227" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:28" ht="18" customHeight="1">
       <c r="A227" s="1">
         <v>46248</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B227" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -36108,15 +36126,15 @@
       <c r="AA227" s="2" t="s">
         <v>3380</v>
       </c>
-      <c r="AB227" s="9" t="s">
+      <c r="AB227" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="228" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" ht="18" customHeight="1">
       <c r="A228" s="1">
         <v>46249</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C228" s="2" t="s">
@@ -36194,15 +36212,15 @@
       <c r="AA228" s="2" t="s">
         <v>3396</v>
       </c>
-      <c r="AB228" s="9" t="s">
+      <c r="AB228" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="229" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:28" ht="18" customHeight="1">
       <c r="A229" s="1">
         <v>46250</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B229" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C229" s="2" t="s">
@@ -36280,15 +36298,15 @@
       <c r="AA229" s="2" t="s">
         <v>3409</v>
       </c>
-      <c r="AB229" s="9" t="s">
+      <c r="AB229" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="230" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:28" ht="18" customHeight="1">
       <c r="A230" s="1">
         <v>46251</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C230" s="2" t="s">
@@ -36366,15 +36384,15 @@
       <c r="AA230" s="2" t="s">
         <v>3425</v>
       </c>
-      <c r="AB230" s="9" t="s">
+      <c r="AB230" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="231" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:28" ht="18" customHeight="1">
       <c r="A231" s="1">
         <v>46252</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B231" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C231" s="2" t="s">
@@ -36452,15 +36470,15 @@
       <c r="AA231" s="2" t="s">
         <v>3439</v>
       </c>
-      <c r="AB231" s="9" t="s">
+      <c r="AB231" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="232" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:28" ht="18" customHeight="1">
       <c r="A232" s="1">
         <v>46253</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C232" s="2" t="s">
@@ -36538,15 +36556,15 @@
       <c r="AA232" s="2" t="s">
         <v>3454</v>
       </c>
-      <c r="AB232" s="9" t="s">
+      <c r="AB232" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="233" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:28" ht="18" customHeight="1">
       <c r="A233" s="1">
         <v>46254</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B233" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C233" s="2" t="s">
@@ -36624,15 +36642,15 @@
       <c r="AA233" s="2" t="s">
         <v>3468</v>
       </c>
-      <c r="AB233" s="9" t="s">
+      <c r="AB233" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="234" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:28" ht="18" customHeight="1">
       <c r="A234" s="1">
         <v>46255</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C234" s="2" t="s">
@@ -36710,15 +36728,15 @@
       <c r="AA234" s="2" t="s">
         <v>3482</v>
       </c>
-      <c r="AB234" s="9" t="s">
+      <c r="AB234" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="235" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:28" ht="18" customHeight="1">
       <c r="A235" s="1">
         <v>46256</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="B235" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C235" s="2" t="s">
@@ -36796,15 +36814,15 @@
       <c r="AA235" s="2" t="s">
         <v>3496</v>
       </c>
-      <c r="AB235" s="9" t="s">
+      <c r="AB235" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="236" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" ht="18" customHeight="1">
       <c r="A236" s="1">
         <v>46257</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="B236" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C236" s="2" t="s">
@@ -36882,15 +36900,15 @@
       <c r="AA236" s="2" t="s">
         <v>3510</v>
       </c>
-      <c r="AB236" s="9" t="s">
+      <c r="AB236" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="237" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:28" ht="18" customHeight="1">
       <c r="A237" s="1">
         <v>46258</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="B237" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C237" s="2" t="s">
@@ -36968,15 +36986,15 @@
       <c r="AA237" s="2" t="s">
         <v>3525</v>
       </c>
-      <c r="AB237" s="9" t="s">
+      <c r="AB237" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="238" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:28" ht="18" customHeight="1">
       <c r="A238" s="1">
         <v>46259</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="B238" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C238" s="2" t="s">
@@ -37054,15 +37072,15 @@
       <c r="AA238" s="2" t="s">
         <v>3539</v>
       </c>
-      <c r="AB238" s="9" t="s">
+      <c r="AB238" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="239" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:28" ht="18" customHeight="1">
       <c r="A239" s="1">
         <v>46260</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="B239" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -37140,15 +37158,15 @@
       <c r="AA239" s="2" t="s">
         <v>3552</v>
       </c>
-      <c r="AB239" s="9" t="s">
+      <c r="AB239" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="240" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:28" ht="18" customHeight="1">
       <c r="A240" s="1">
         <v>46261</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C240" s="2" t="s">
@@ -37226,15 +37244,15 @@
       <c r="AA240" s="2" t="s">
         <v>3567</v>
       </c>
-      <c r="AB240" s="9" t="s">
+      <c r="AB240" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="241" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:28" ht="18" customHeight="1">
       <c r="A241" s="1">
         <v>46262</v>
       </c>
-      <c r="B241" s="2" t="s">
+      <c r="B241" s="9" t="s">
         <v>3149</v>
       </c>
       <c r="C241" s="2" t="s">
@@ -37312,15 +37330,15 @@
       <c r="AA241" s="2" t="s">
         <v>3581</v>
       </c>
-      <c r="AB241" s="9" t="s">
+      <c r="AB241" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="242" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:28" ht="18" customHeight="1">
       <c r="A242" s="1">
         <v>46263</v>
       </c>
-      <c r="B242" s="2" t="s">
+      <c r="B242" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C242" s="2" t="s">
@@ -37398,15 +37416,15 @@
       <c r="AA242" s="2" t="s">
         <v>3597</v>
       </c>
-      <c r="AB242" s="9" t="s">
+      <c r="AB242" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="243" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:28" ht="18" customHeight="1">
       <c r="A243" s="1">
         <v>46264</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="B243" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -37484,15 +37502,15 @@
       <c r="AA243" s="2" t="s">
         <v>3612</v>
       </c>
-      <c r="AB243" s="9" t="s">
+      <c r="AB243" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="244" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:28" ht="18" customHeight="1">
       <c r="A244" s="1">
         <v>46265</v>
       </c>
-      <c r="B244" s="2" t="s">
+      <c r="B244" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C244" s="2" t="s">
@@ -37570,15 +37588,15 @@
       <c r="AA244" s="2" t="s">
         <v>3626</v>
       </c>
-      <c r="AB244" s="9" t="s">
+      <c r="AB244" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="245" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:28" ht="18" customHeight="1">
       <c r="A245" s="1">
         <v>46266</v>
       </c>
-      <c r="B245" s="2" t="s">
+      <c r="B245" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C245" s="2" t="s">
@@ -37656,15 +37674,15 @@
       <c r="AA245" s="2" t="s">
         <v>3642</v>
       </c>
-      <c r="AB245" s="9" t="s">
+      <c r="AB245" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="246" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:28" ht="18" customHeight="1">
       <c r="A246" s="1">
         <v>46267</v>
       </c>
-      <c r="B246" s="2" t="s">
+      <c r="B246" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C246" s="2" t="s">
@@ -37742,15 +37760,15 @@
       <c r="AA246" s="2" t="s">
         <v>3656</v>
       </c>
-      <c r="AB246" s="9" t="s">
+      <c r="AB246" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="247" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:28" ht="18" customHeight="1">
       <c r="A247" s="1">
         <v>46268</v>
       </c>
-      <c r="B247" s="2" t="s">
+      <c r="B247" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C247" s="2" t="s">
@@ -37828,15 +37846,15 @@
       <c r="AA247" s="2" t="s">
         <v>3671</v>
       </c>
-      <c r="AB247" s="9" t="s">
+      <c r="AB247" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="248" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:28" ht="18" customHeight="1">
       <c r="A248" s="1">
         <v>46269</v>
       </c>
-      <c r="B248" s="2" t="s">
+      <c r="B248" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C248" s="2" t="s">
@@ -37914,15 +37932,15 @@
       <c r="AA248" s="2" t="s">
         <v>3685</v>
       </c>
-      <c r="AB248" s="9" t="s">
+      <c r="AB248" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="249" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:28" ht="18" customHeight="1">
       <c r="A249" s="1">
         <v>46270</v>
       </c>
-      <c r="B249" s="2" t="s">
+      <c r="B249" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C249" s="2" t="s">
@@ -38000,15 +38018,15 @@
       <c r="AA249" s="2" t="s">
         <v>3700</v>
       </c>
-      <c r="AB249" s="9" t="s">
+      <c r="AB249" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="250" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:28" ht="18" customHeight="1">
       <c r="A250" s="1">
         <v>46271</v>
       </c>
-      <c r="B250" s="2" t="s">
+      <c r="B250" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C250" s="2" t="s">
@@ -38086,15 +38104,15 @@
       <c r="AA250" s="2" t="s">
         <v>3715</v>
       </c>
-      <c r="AB250" s="9" t="s">
+      <c r="AB250" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="251" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:28" ht="18" customHeight="1">
       <c r="A251" s="1">
         <v>46272</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="B251" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C251" s="2" t="s">
@@ -38172,15 +38190,15 @@
       <c r="AA251" s="2" t="s">
         <v>3729</v>
       </c>
-      <c r="AB251" s="9" t="s">
+      <c r="AB251" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="252" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:28" ht="18" customHeight="1">
       <c r="A252" s="1">
         <v>46273</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="B252" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C252" s="2" t="s">
@@ -38258,15 +38276,15 @@
       <c r="AA252" s="2" t="s">
         <v>3743</v>
       </c>
-      <c r="AB252" s="9" t="s">
+      <c r="AB252" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="253" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:28" ht="18" customHeight="1">
       <c r="A253" s="1">
         <v>46274</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="B253" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C253" s="2" t="s">
@@ -38344,15 +38362,15 @@
       <c r="AA253" s="2" t="s">
         <v>3757</v>
       </c>
-      <c r="AB253" s="9" t="s">
+      <c r="AB253" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="254" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:28" ht="18" customHeight="1">
       <c r="A254" s="1">
         <v>46275</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="B254" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C254" s="2" t="s">
@@ -38430,15 +38448,15 @@
       <c r="AA254" s="2" t="s">
         <v>3770</v>
       </c>
-      <c r="AB254" s="9" t="s">
+      <c r="AB254" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="255" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:28" ht="18" customHeight="1">
       <c r="A255" s="1">
         <v>46276</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="B255" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C255" s="2" t="s">
@@ -38516,15 +38534,15 @@
       <c r="AA255" s="2" t="s">
         <v>3785</v>
       </c>
-      <c r="AB255" s="9" t="s">
+      <c r="AB255" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="256" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:28" ht="18" customHeight="1">
       <c r="A256" s="1">
         <v>46277</v>
       </c>
-      <c r="B256" s="2" t="s">
+      <c r="B256" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C256" s="2" t="s">
@@ -38602,15 +38620,15 @@
       <c r="AA256" s="2" t="s">
         <v>3799</v>
       </c>
-      <c r="AB256" s="9" t="s">
+      <c r="AB256" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="257" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:28" ht="18" customHeight="1">
       <c r="A257" s="1">
         <v>46278</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="B257" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C257" s="2" t="s">
@@ -38688,15 +38706,15 @@
       <c r="AA257" s="2" t="s">
         <v>3814</v>
       </c>
-      <c r="AB257" s="9" t="s">
+      <c r="AB257" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="258" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:28" ht="18" customHeight="1">
       <c r="A258" s="1">
         <v>46279</v>
       </c>
-      <c r="B258" s="2" t="s">
+      <c r="B258" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C258" s="2" t="s">
@@ -38774,15 +38792,15 @@
       <c r="AA258" s="2" t="s">
         <v>3827</v>
       </c>
-      <c r="AB258" s="9" t="s">
+      <c r="AB258" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="259" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:28" ht="18" customHeight="1">
       <c r="A259" s="1">
         <v>46280</v>
       </c>
-      <c r="B259" s="2" t="s">
+      <c r="B259" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C259" s="2" t="s">
@@ -38860,15 +38878,15 @@
       <c r="AA259" s="2" t="s">
         <v>3841</v>
       </c>
-      <c r="AB259" s="9" t="s">
+      <c r="AB259" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="260" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:28" ht="18" customHeight="1">
       <c r="A260" s="1">
         <v>46281</v>
       </c>
-      <c r="B260" s="2" t="s">
+      <c r="B260" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C260" s="2" t="s">
@@ -38946,15 +38964,15 @@
       <c r="AA260" s="2" t="s">
         <v>3856</v>
       </c>
-      <c r="AB260" s="9" t="s">
+      <c r="AB260" s="2" t="s">
         <v>3410</v>
       </c>
     </row>
-    <row r="261" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:28" ht="18" customHeight="1">
       <c r="A261" s="1">
         <v>46282</v>
       </c>
-      <c r="B261" s="2" t="s">
+      <c r="B261" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C261" s="2" t="s">
@@ -39032,15 +39050,15 @@
       <c r="AA261" s="2" t="s">
         <v>3870</v>
       </c>
-      <c r="AB261" s="9" t="s">
+      <c r="AB261" s="2" t="s">
         <v>3871</v>
       </c>
     </row>
-    <row r="262" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:28" ht="18" customHeight="1">
       <c r="A262" s="1">
         <v>46283</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="B262" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C262" s="2" t="s">
@@ -39118,15 +39136,15 @@
       <c r="AA262" s="2" t="s">
         <v>3885</v>
       </c>
-      <c r="AB262" s="9" t="s">
+      <c r="AB262" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="263" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:28" ht="18" customHeight="1">
       <c r="A263" s="1">
         <v>46284</v>
       </c>
-      <c r="B263" s="2" t="s">
+      <c r="B263" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C263" s="2" t="s">
@@ -39204,15 +39222,15 @@
       <c r="AA263" s="2" t="s">
         <v>3898</v>
       </c>
-      <c r="AB263" s="9" t="s">
+      <c r="AB263" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="264" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:28" ht="18" customHeight="1">
       <c r="A264" s="1">
         <v>46285</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="B264" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C264" s="2" t="s">
@@ -39290,15 +39308,15 @@
       <c r="AA264" s="2" t="s">
         <v>3912</v>
       </c>
-      <c r="AB264" s="9" t="s">
+      <c r="AB264" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="265" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:28" ht="18" customHeight="1">
       <c r="A265" s="1">
         <v>46286</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="B265" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C265" s="2" t="s">
@@ -39376,15 +39394,15 @@
       <c r="AA265" s="2" t="s">
         <v>3927</v>
       </c>
-      <c r="AB265" s="9" t="s">
+      <c r="AB265" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="266" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:28" ht="18" customHeight="1">
       <c r="A266" s="1">
         <v>46287</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B266" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C266" s="2" t="s">
@@ -39462,15 +39480,15 @@
       <c r="AA266" s="2" t="s">
         <v>3940</v>
       </c>
-      <c r="AB266" s="9" t="s">
+      <c r="AB266" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="267" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:28" ht="18" customHeight="1">
       <c r="A267" s="1">
         <v>46288</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="B267" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C267" s="2" t="s">
@@ -39548,15 +39566,15 @@
       <c r="AA267" s="2" t="s">
         <v>3955</v>
       </c>
-      <c r="AB267" s="9" t="s">
+      <c r="AB267" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="268" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:28" ht="18" customHeight="1">
       <c r="A268" s="1">
         <v>46289</v>
       </c>
-      <c r="B268" s="2" t="s">
+      <c r="B268" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C268" s="2" t="s">
@@ -39634,15 +39652,15 @@
       <c r="AA268" s="2" t="s">
         <v>3969</v>
       </c>
-      <c r="AB268" s="9" t="s">
+      <c r="AB268" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="269" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:28" ht="18" customHeight="1">
       <c r="A269" s="1">
         <v>46290</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="B269" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C269" s="2" t="s">
@@ -39720,15 +39738,15 @@
       <c r="AA269" s="2" t="s">
         <v>3983</v>
       </c>
-      <c r="AB269" s="9" t="s">
+      <c r="AB269" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="270" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:28" ht="18" customHeight="1">
       <c r="A270" s="1">
         <v>46291</v>
       </c>
-      <c r="B270" s="2" t="s">
+      <c r="B270" s="9" t="s">
         <v>3582</v>
       </c>
       <c r="C270" s="2" t="s">
@@ -39806,15 +39824,15 @@
       <c r="AA270" s="2" t="s">
         <v>3997</v>
       </c>
-      <c r="AB270" s="9" t="s">
+      <c r="AB270" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="271" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:28" ht="18" customHeight="1">
       <c r="A271" s="1">
         <v>46292</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="B271" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C271" s="2" t="s">
@@ -39892,15 +39910,15 @@
       <c r="AA271" s="2" t="s">
         <v>4012</v>
       </c>
-      <c r="AB271" s="9" t="s">
+      <c r="AB271" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="272" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:28" ht="18" customHeight="1">
       <c r="A272" s="1">
         <v>46293</v>
       </c>
-      <c r="B272" s="2" t="s">
+      <c r="B272" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C272" s="2" t="s">
@@ -39978,15 +39996,15 @@
       <c r="AA272" s="2" t="s">
         <v>4026</v>
       </c>
-      <c r="AB272" s="9" t="s">
+      <c r="AB272" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="273" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" ht="18" customHeight="1">
       <c r="A273" s="1">
         <v>46294</v>
       </c>
-      <c r="B273" s="2" t="s">
+      <c r="B273" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C273" s="2" t="s">
@@ -40064,15 +40082,15 @@
       <c r="AA273" s="2" t="s">
         <v>4041</v>
       </c>
-      <c r="AB273" s="9" t="s">
+      <c r="AB273" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="274" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" ht="18" customHeight="1">
       <c r="A274" s="1">
         <v>46295</v>
       </c>
-      <c r="B274" s="2" t="s">
+      <c r="B274" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C274" s="2" t="s">
@@ -40150,15 +40168,15 @@
       <c r="AA274" s="2" t="s">
         <v>4057</v>
       </c>
-      <c r="AB274" s="9" t="s">
+      <c r="AB274" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="275" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:28" ht="18" customHeight="1">
       <c r="A275" s="1">
         <v>46296</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="B275" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C275" s="2" t="s">
@@ -40236,15 +40254,15 @@
       <c r="AA275" s="2" t="s">
         <v>4071</v>
       </c>
-      <c r="AB275" s="9" t="s">
+      <c r="AB275" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="276" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:28" ht="18" customHeight="1">
       <c r="A276" s="1">
         <v>46297</v>
       </c>
-      <c r="B276" s="2" t="s">
+      <c r="B276" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C276" s="2" t="s">
@@ -40322,15 +40340,15 @@
       <c r="AA276" s="2" t="s">
         <v>4087</v>
       </c>
-      <c r="AB276" s="9" t="s">
+      <c r="AB276" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="277" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:28" ht="18" customHeight="1">
       <c r="A277" s="1">
         <v>46298</v>
       </c>
-      <c r="B277" s="2" t="s">
+      <c r="B277" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C277" s="2" t="s">
@@ -40408,15 +40426,15 @@
       <c r="AA277" s="2" t="s">
         <v>4101</v>
       </c>
-      <c r="AB277" s="9" t="s">
+      <c r="AB277" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="278" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:28" ht="18" customHeight="1">
       <c r="A278" s="1">
         <v>46299</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="B278" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C278" s="2" t="s">
@@ -40494,15 +40512,15 @@
       <c r="AA278" s="2" t="s">
         <v>4118</v>
       </c>
-      <c r="AB278" s="9" t="s">
+      <c r="AB278" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="279" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:28" ht="18" customHeight="1">
       <c r="A279" s="1">
         <v>46300</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="B279" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C279" s="2" t="s">
@@ -40580,15 +40598,15 @@
       <c r="AA279" s="2" t="s">
         <v>4132</v>
       </c>
-      <c r="AB279" s="9" t="s">
+      <c r="AB279" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="280" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:28" ht="18" customHeight="1">
       <c r="A280" s="1">
         <v>46301</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="B280" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C280" s="2" t="s">
@@ -40666,15 +40684,15 @@
       <c r="AA280" s="2" t="s">
         <v>4146</v>
       </c>
-      <c r="AB280" s="9" t="s">
+      <c r="AB280" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="281" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:28" ht="18" customHeight="1">
       <c r="A281" s="1">
         <v>46302</v>
       </c>
-      <c r="B281" s="2" t="s">
+      <c r="B281" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C281" s="2" t="s">
@@ -40752,15 +40770,15 @@
       <c r="AA281" s="2" t="s">
         <v>4161</v>
       </c>
-      <c r="AB281" s="9" t="s">
+      <c r="AB281" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="282" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:28" ht="18" customHeight="1">
       <c r="A282" s="1">
         <v>46303</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="B282" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C282" s="2" t="s">
@@ -40838,15 +40856,15 @@
       <c r="AA282" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="AB282" s="9" t="s">
+      <c r="AB282" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="283" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:28" ht="18" customHeight="1">
       <c r="A283" s="1">
         <v>46304</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="B283" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C283" s="2" t="s">
@@ -40924,15 +40942,15 @@
       <c r="AA283" s="2" t="s">
         <v>4188</v>
       </c>
-      <c r="AB283" s="9" t="s">
+      <c r="AB283" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="284" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:28" ht="18" customHeight="1">
       <c r="A284" s="1">
         <v>46305</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="B284" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C284" s="2" t="s">
@@ -41010,15 +41028,15 @@
       <c r="AA284" s="2" t="s">
         <v>4202</v>
       </c>
-      <c r="AB284" s="9" t="s">
+      <c r="AB284" s="2" t="s">
         <v>3984</v>
       </c>
     </row>
-    <row r="285" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:28" ht="18" customHeight="1">
       <c r="A285" s="1">
         <v>46306</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="B285" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C285" s="2" t="s">
@@ -41096,15 +41114,15 @@
       <c r="AA285" s="2" t="s">
         <v>4216</v>
       </c>
-      <c r="AB285" s="9" t="s">
+      <c r="AB285" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
-    <row r="286" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:28" ht="18" customHeight="1">
       <c r="A286" s="1">
         <v>46307</v>
       </c>
-      <c r="B286" s="2" t="s">
+      <c r="B286" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C286" s="2" t="s">
@@ -41182,15 +41200,15 @@
       <c r="AA286" s="2" t="s">
         <v>4231</v>
       </c>
-      <c r="AB286" s="9" t="s">
+      <c r="AB286" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
-    <row r="287" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:28" ht="18" customHeight="1">
       <c r="A287" s="1">
         <v>46308</v>
       </c>
-      <c r="B287" s="2" t="s">
+      <c r="B287" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C287" s="2" t="s">
@@ -41268,15 +41286,15 @@
       <c r="AA287" s="2" t="s">
         <v>4246</v>
       </c>
-      <c r="AB287" s="9" t="s">
+      <c r="AB287" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
-    <row r="288" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:28" ht="18" customHeight="1">
       <c r="A288" s="1">
         <v>46309</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B288" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C288" s="2" t="s">
@@ -41354,15 +41372,15 @@
       <c r="AA288" s="2" t="s">
         <v>4260</v>
       </c>
-      <c r="AB288" s="9" t="s">
+      <c r="AB288" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
-    <row r="289" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:28" ht="18" customHeight="1">
       <c r="A289" s="1">
         <v>46310</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="B289" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C289" s="2" t="s">
@@ -41440,15 +41458,15 @@
       <c r="AA289" s="2" t="s">
         <v>4273</v>
       </c>
-      <c r="AB289" s="9" t="s">
+      <c r="AB289" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
-    <row r="290" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:28" ht="18" customHeight="1">
       <c r="A290" s="1">
         <v>46311</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="B290" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C290" s="2" t="s">
@@ -41526,15 +41544,15 @@
       <c r="AA290" s="2" t="s">
         <v>4286</v>
       </c>
-      <c r="AB290" s="9" t="s">
+      <c r="AB290" s="2" t="s">
         <v>4217</v>
       </c>
     </row>
-    <row r="291" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:28" ht="18" customHeight="1">
       <c r="A291" s="1">
         <v>46312</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="B291" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C291" s="2" t="s">
@@ -41612,15 +41630,15 @@
       <c r="AA291" s="2" t="s">
         <v>4300</v>
       </c>
-      <c r="AB291" s="9" t="s">
+      <c r="AB291" s="2" t="s">
         <v>4301</v>
       </c>
     </row>
-    <row r="292" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:28" ht="18" customHeight="1">
       <c r="A292" s="1">
         <v>46313</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="B292" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C292" s="2" t="s">
@@ -41698,15 +41716,15 @@
       <c r="AA292" s="2" t="s">
         <v>4316</v>
       </c>
-      <c r="AB292" s="9" t="s">
+      <c r="AB292" s="2" t="s">
         <v>4301</v>
       </c>
     </row>
-    <row r="293" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:28" ht="18" customHeight="1">
       <c r="A293" s="1">
         <v>46314</v>
       </c>
-      <c r="B293" s="2" t="s">
+      <c r="B293" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C293" s="2" t="s">
@@ -41784,15 +41802,15 @@
       <c r="AA293" s="2" t="s">
         <v>4329</v>
       </c>
-      <c r="AB293" s="9" t="s">
+      <c r="AB293" s="2" t="s">
         <v>4301</v>
       </c>
     </row>
-    <row r="294" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:28" ht="18" customHeight="1">
       <c r="A294" s="1">
         <v>46315</v>
       </c>
-      <c r="B294" s="2" t="s">
+      <c r="B294" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C294" s="2" t="s">
@@ -41870,15 +41888,15 @@
       <c r="AA294" s="2" t="s">
         <v>4344</v>
       </c>
-      <c r="AB294" s="9" t="s">
+      <c r="AB294" s="2" t="s">
         <v>4345</v>
       </c>
     </row>
-    <row r="295" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:28" ht="18" customHeight="1">
       <c r="A295" s="1">
         <v>46316</v>
       </c>
-      <c r="B295" s="2" t="s">
+      <c r="B295" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C295" s="2" t="s">
@@ -41956,15 +41974,15 @@
       <c r="AA295" s="2" t="s">
         <v>4359</v>
       </c>
-      <c r="AB295" s="9" t="s">
+      <c r="AB295" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="296" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:28" ht="18" customHeight="1">
       <c r="A296" s="1">
         <v>46317</v>
       </c>
-      <c r="B296" s="2" t="s">
+      <c r="B296" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C296" s="2" t="s">
@@ -42042,15 +42060,15 @@
       <c r="AA296" s="2" t="s">
         <v>4374</v>
       </c>
-      <c r="AB296" s="9" t="s">
+      <c r="AB296" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="297" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:28" ht="18" customHeight="1">
       <c r="A297" s="1">
         <v>46318</v>
       </c>
-      <c r="B297" s="2" t="s">
+      <c r="B297" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C297" s="2" t="s">
@@ -42128,15 +42146,15 @@
       <c r="AA297" s="2" t="s">
         <v>4389</v>
       </c>
-      <c r="AB297" s="9" t="s">
+      <c r="AB297" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="298" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:28" ht="18" customHeight="1">
       <c r="A298" s="1">
         <v>46319</v>
       </c>
-      <c r="B298" s="2" t="s">
+      <c r="B298" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C298" s="2" t="s">
@@ -42214,15 +42232,15 @@
       <c r="AA298" s="2" t="s">
         <v>4403</v>
       </c>
-      <c r="AB298" s="9" t="s">
+      <c r="AB298" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="299" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:28" ht="18" customHeight="1">
       <c r="A299" s="1">
         <v>46320</v>
       </c>
-      <c r="B299" s="2" t="s">
+      <c r="B299" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C299" s="2" t="s">
@@ -42300,15 +42318,15 @@
       <c r="AA299" s="2" t="s">
         <v>4417</v>
       </c>
-      <c r="AB299" s="9" t="s">
+      <c r="AB299" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="300" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:28" ht="18" customHeight="1">
       <c r="A300" s="1">
         <v>46321</v>
       </c>
-      <c r="B300" s="2" t="s">
+      <c r="B300" s="9" t="s">
         <v>3998</v>
       </c>
       <c r="C300" s="2" t="s">
@@ -42386,15 +42404,15 @@
       <c r="AA300" s="2" t="s">
         <v>4430</v>
       </c>
-      <c r="AB300" s="9" t="s">
+      <c r="AB300" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="301" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:28" ht="18" customHeight="1">
       <c r="A301" s="1">
         <v>46322</v>
       </c>
-      <c r="B301" s="2" t="s">
+      <c r="B301" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C301" s="2" t="s">
@@ -42472,15 +42490,15 @@
       <c r="AA301" s="2" t="s">
         <v>4448</v>
       </c>
-      <c r="AB301" s="9" t="s">
+      <c r="AB301" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="302" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:28" ht="18" customHeight="1">
       <c r="A302" s="1">
         <v>46323</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="B302" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C302" s="2" t="s">
@@ -42558,15 +42576,15 @@
       <c r="AA302" s="2" t="s">
         <v>4462</v>
       </c>
-      <c r="AB302" s="9" t="s">
+      <c r="AB302" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="303" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:28" ht="18" customHeight="1">
       <c r="A303" s="1">
         <v>46324</v>
       </c>
-      <c r="B303" s="2" t="s">
+      <c r="B303" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C303" s="2" t="s">
@@ -42644,15 +42662,15 @@
       <c r="AA303" s="2" t="s">
         <v>4478</v>
       </c>
-      <c r="AB303" s="9" t="s">
+      <c r="AB303" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="304" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:28" ht="18" customHeight="1">
       <c r="A304" s="1">
         <v>46325</v>
       </c>
-      <c r="B304" s="2" t="s">
+      <c r="B304" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C304" s="2" t="s">
@@ -42730,15 +42748,15 @@
       <c r="AA304" s="2" t="s">
         <v>4491</v>
       </c>
-      <c r="AB304" s="9" t="s">
+      <c r="AB304" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="305" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:28" ht="18" customHeight="1">
       <c r="A305" s="1">
         <v>46326</v>
       </c>
-      <c r="B305" s="2" t="s">
+      <c r="B305" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C305" s="2" t="s">
@@ -42816,15 +42834,15 @@
       <c r="AA305" s="2" t="s">
         <v>4506</v>
       </c>
-      <c r="AB305" s="9" t="s">
+      <c r="AB305" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="306" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:28" ht="18" customHeight="1">
       <c r="A306" s="1">
         <v>46327</v>
       </c>
-      <c r="B306" s="2" t="s">
+      <c r="B306" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C306" s="2" t="s">
@@ -42902,15 +42920,15 @@
       <c r="AA306" s="2" t="s">
         <v>4521</v>
       </c>
-      <c r="AB306" s="9" t="s">
+      <c r="AB306" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="307" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:28" ht="18" customHeight="1">
       <c r="A307" s="1">
         <v>46328</v>
       </c>
-      <c r="B307" s="2" t="s">
+      <c r="B307" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C307" s="2" t="s">
@@ -42988,15 +43006,15 @@
       <c r="AA307" s="2" t="s">
         <v>4535</v>
       </c>
-      <c r="AB307" s="9" t="s">
+      <c r="AB307" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="308" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:28" ht="18" customHeight="1">
       <c r="A308" s="1">
         <v>46329</v>
       </c>
-      <c r="B308" s="2" t="s">
+      <c r="B308" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C308" s="2" t="s">
@@ -43074,15 +43092,15 @@
       <c r="AA308" s="2" t="s">
         <v>4548</v>
       </c>
-      <c r="AB308" s="9" t="s">
+      <c r="AB308" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="309" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:28" ht="18" customHeight="1">
       <c r="A309" s="1">
         <v>46330</v>
       </c>
-      <c r="B309" s="2" t="s">
+      <c r="B309" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C309" s="2" t="s">
@@ -43160,15 +43178,15 @@
       <c r="AA309" s="2" t="s">
         <v>4562</v>
       </c>
-      <c r="AB309" s="9" t="s">
+      <c r="AB309" s="2" t="s">
         <v>4360</v>
       </c>
     </row>
-    <row r="310" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:28" ht="18" customHeight="1">
       <c r="A310" s="1">
         <v>46331</v>
       </c>
-      <c r="B310" s="2" t="s">
+      <c r="B310" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C310" s="2" t="s">
@@ -43246,15 +43264,15 @@
       <c r="AA310" s="2" t="s">
         <v>4577</v>
       </c>
-      <c r="AB310" s="9" t="s">
+      <c r="AB310" s="2" t="s">
         <v>4578</v>
       </c>
     </row>
-    <row r="311" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:28" ht="18" customHeight="1">
       <c r="A311" s="1">
         <v>46332</v>
       </c>
-      <c r="B311" s="2" t="s">
+      <c r="B311" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C311" s="2" t="s">
@@ -43332,15 +43350,15 @@
       <c r="AA311" s="2" t="s">
         <v>4593</v>
       </c>
-      <c r="AB311" s="9" t="s">
+      <c r="AB311" s="2" t="s">
         <v>4594</v>
       </c>
     </row>
-    <row r="312" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:28" ht="18" customHeight="1">
       <c r="A312" s="1">
         <v>46333</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="B312" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C312" s="2" t="s">
@@ -43418,15 +43436,15 @@
       <c r="AA312" s="2" t="s">
         <v>4609</v>
       </c>
-      <c r="AB312" s="9" t="s">
+      <c r="AB312" s="2" t="s">
         <v>4594</v>
       </c>
     </row>
-    <row r="313" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:28" ht="18" customHeight="1">
       <c r="A313" s="1">
         <v>46334</v>
       </c>
-      <c r="B313" s="2" t="s">
+      <c r="B313" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C313" s="2" t="s">
@@ -43504,15 +43522,15 @@
       <c r="AA313" s="2" t="s">
         <v>4623</v>
       </c>
-      <c r="AB313" s="9" t="s">
+      <c r="AB313" s="2" t="s">
         <v>4594</v>
       </c>
     </row>
-    <row r="314" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:28" ht="18" customHeight="1">
       <c r="A314" s="1">
         <v>46335</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="B314" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C314" s="2" t="s">
@@ -43590,15 +43608,15 @@
       <c r="AA314" s="2" t="s">
         <v>4638</v>
       </c>
-      <c r="AB314" s="9" t="s">
+      <c r="AB314" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="315" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:28" ht="18" customHeight="1">
       <c r="A315" s="1">
         <v>46336</v>
       </c>
-      <c r="B315" s="2" t="s">
+      <c r="B315" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C315" s="2" t="s">
@@ -43676,15 +43694,15 @@
       <c r="AA315" s="2" t="s">
         <v>4652</v>
       </c>
-      <c r="AB315" s="9" t="s">
+      <c r="AB315" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="316" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:28" ht="18" customHeight="1">
       <c r="A316" s="1">
         <v>46337</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="B316" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C316" s="2" t="s">
@@ -43762,15 +43780,15 @@
       <c r="AA316" s="2" t="s">
         <v>4666</v>
       </c>
-      <c r="AB316" s="9" t="s">
+      <c r="AB316" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="317" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:28" ht="18" customHeight="1">
       <c r="A317" s="1">
         <v>46338</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="B317" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C317" s="2" t="s">
@@ -43848,15 +43866,15 @@
       <c r="AA317" s="2" t="s">
         <v>4680</v>
       </c>
-      <c r="AB317" s="9" t="s">
+      <c r="AB317" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="318" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:28" ht="18" customHeight="1">
       <c r="A318" s="1">
         <v>46339</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="B318" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C318" s="2" t="s">
@@ -43934,15 +43952,15 @@
       <c r="AA318" s="2" t="s">
         <v>4693</v>
       </c>
-      <c r="AB318" s="9" t="s">
+      <c r="AB318" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="319" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:28" ht="18" customHeight="1">
       <c r="A319" s="1">
         <v>46340</v>
       </c>
-      <c r="B319" s="2" t="s">
+      <c r="B319" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C319" s="2" t="s">
@@ -44020,15 +44038,15 @@
       <c r="AA319" s="2" t="s">
         <v>4707</v>
       </c>
-      <c r="AB319" s="9" t="s">
+      <c r="AB319" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="320" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:28" ht="18" customHeight="1">
       <c r="A320" s="1">
         <v>46341</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="B320" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C320" s="2" t="s">
@@ -44106,15 +44124,15 @@
       <c r="AA320" s="2" t="s">
         <v>4721</v>
       </c>
-      <c r="AB320" s="9" t="s">
+      <c r="AB320" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="321" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:28" ht="18" customHeight="1">
       <c r="A321" s="1">
         <v>46342</v>
       </c>
-      <c r="B321" s="2" t="s">
+      <c r="B321" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C321" s="2" t="s">
@@ -44192,15 +44210,15 @@
       <c r="AA321" s="2" t="s">
         <v>4735</v>
       </c>
-      <c r="AB321" s="9" t="s">
+      <c r="AB321" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="322" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:28" ht="18" customHeight="1">
       <c r="A322" s="1">
         <v>46343</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="B322" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C322" s="2" t="s">
@@ -44278,15 +44296,15 @@
       <c r="AA322" s="2" t="s">
         <v>4750</v>
       </c>
-      <c r="AB322" s="9" t="s">
+      <c r="AB322" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="323" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:28" ht="18" customHeight="1">
       <c r="A323" s="1">
         <v>46344</v>
       </c>
-      <c r="B323" s="2" t="s">
+      <c r="B323" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C323" s="2" t="s">
@@ -44364,15 +44382,15 @@
       <c r="AA323" s="2" t="s">
         <v>4764</v>
       </c>
-      <c r="AB323" s="9" t="s">
+      <c r="AB323" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="324" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:28" ht="18" customHeight="1">
       <c r="A324" s="1">
         <v>46345</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="B324" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C324" s="2" t="s">
@@ -44450,15 +44468,15 @@
       <c r="AA324" s="2" t="s">
         <v>4779</v>
       </c>
-      <c r="AB324" s="9" t="s">
+      <c r="AB324" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="325" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:28" ht="18" customHeight="1">
       <c r="A325" s="1">
         <v>46346</v>
       </c>
-      <c r="B325" s="2" t="s">
+      <c r="B325" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C325" s="2" t="s">
@@ -44536,15 +44554,15 @@
       <c r="AA325" s="2" t="s">
         <v>4793</v>
       </c>
-      <c r="AB325" s="9" t="s">
+      <c r="AB325" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="326" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:28" ht="18" customHeight="1">
       <c r="A326" s="1">
         <v>46347</v>
       </c>
-      <c r="B326" s="2" t="s">
+      <c r="B326" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C326" s="2" t="s">
@@ -44622,15 +44640,15 @@
       <c r="AA326" s="2" t="s">
         <v>4807</v>
       </c>
-      <c r="AB326" s="9" t="s">
+      <c r="AB326" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="327" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:28" ht="18" customHeight="1">
       <c r="A327" s="1">
         <v>46348</v>
       </c>
-      <c r="B327" s="2" t="s">
+      <c r="B327" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C327" s="2" t="s">
@@ -44708,15 +44726,15 @@
       <c r="AA327" s="2" t="s">
         <v>4821</v>
       </c>
-      <c r="AB327" s="9" t="s">
+      <c r="AB327" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="328" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:28" ht="18" customHeight="1">
       <c r="A328" s="1">
         <v>46349</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="B328" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C328" s="2" t="s">
@@ -44794,15 +44812,15 @@
       <c r="AA328" s="2" t="s">
         <v>4835</v>
       </c>
-      <c r="AB328" s="9" t="s">
+      <c r="AB328" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="329" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:28" ht="18" customHeight="1">
       <c r="A329" s="1">
         <v>46350</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="B329" s="9" t="s">
         <v>4431</v>
       </c>
       <c r="C329" s="2" t="s">
@@ -44880,15 +44898,15 @@
       <c r="AA329" s="2" t="s">
         <v>4850</v>
       </c>
-      <c r="AB329" s="9" t="s">
+      <c r="AB329" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="330" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:28" ht="18" customHeight="1">
       <c r="A330" s="1">
         <v>46351</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="B330" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C330" s="2" t="s">
@@ -44966,15 +44984,15 @@
       <c r="AA330" s="2" t="s">
         <v>4865</v>
       </c>
-      <c r="AB330" s="9" t="s">
+      <c r="AB330" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="331" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:28" ht="18" customHeight="1">
       <c r="A331" s="1">
         <v>46352</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="B331" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C331" s="2" t="s">
@@ -45052,15 +45070,15 @@
       <c r="AA331" s="2" t="s">
         <v>4880</v>
       </c>
-      <c r="AB331" s="9" t="s">
+      <c r="AB331" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="332" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:28" ht="18" customHeight="1">
       <c r="A332" s="1">
         <v>46353</v>
       </c>
-      <c r="B332" s="2" t="s">
+      <c r="B332" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C332" s="2" t="s">
@@ -45138,15 +45156,15 @@
       <c r="AA332" s="2" t="s">
         <v>4895</v>
       </c>
-      <c r="AB332" s="9" t="s">
+      <c r="AB332" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="333" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:28" ht="18" customHeight="1">
       <c r="A333" s="1">
         <v>46354</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="B333" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C333" s="2" t="s">
@@ -45224,15 +45242,15 @@
       <c r="AA333" s="2" t="s">
         <v>4910</v>
       </c>
-      <c r="AB333" s="9" t="s">
+      <c r="AB333" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="334" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:28" ht="18" customHeight="1">
       <c r="A334" s="1">
         <v>46355</v>
       </c>
-      <c r="B334" s="2" t="s">
+      <c r="B334" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C334" s="2" t="s">
@@ -45310,15 +45328,15 @@
       <c r="AA334" s="2" t="s">
         <v>4924</v>
       </c>
-      <c r="AB334" s="9" t="s">
+      <c r="AB334" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="335" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:28" ht="18" customHeight="1">
       <c r="A335" s="1">
         <v>46356</v>
       </c>
-      <c r="B335" s="2" t="s">
+      <c r="B335" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C335" s="2" t="s">
@@ -45396,15 +45414,15 @@
       <c r="AA335" s="2" t="s">
         <v>4940</v>
       </c>
-      <c r="AB335" s="9" t="s">
+      <c r="AB335" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="336" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:28" ht="18" customHeight="1">
       <c r="A336" s="1">
         <v>46357</v>
       </c>
-      <c r="B336" s="2" t="s">
+      <c r="B336" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C336" s="2" t="s">
@@ -45482,15 +45500,15 @@
       <c r="AA336" s="2" t="s">
         <v>4954</v>
       </c>
-      <c r="AB336" s="9" t="s">
+      <c r="AB336" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="337" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:28" ht="18" customHeight="1">
       <c r="A337" s="1">
         <v>46358</v>
       </c>
-      <c r="B337" s="2" t="s">
+      <c r="B337" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C337" s="2" t="s">
@@ -45568,15 +45586,15 @@
       <c r="AA337" s="2" t="s">
         <v>4969</v>
       </c>
-      <c r="AB337" s="9" t="s">
+      <c r="AB337" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="338" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:28" ht="18" customHeight="1">
       <c r="A338" s="1">
         <v>46359</v>
       </c>
-      <c r="B338" s="2" t="s">
+      <c r="B338" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C338" s="2" t="s">
@@ -45654,15 +45672,15 @@
       <c r="AA338" s="2" t="s">
         <v>4982</v>
       </c>
-      <c r="AB338" s="9" t="s">
+      <c r="AB338" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="339" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:28" ht="18" customHeight="1">
       <c r="A339" s="1">
         <v>46360</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="B339" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C339" s="2" t="s">
@@ -45740,15 +45758,15 @@
       <c r="AA339" s="2" t="s">
         <v>4997</v>
       </c>
-      <c r="AB339" s="9" t="s">
+      <c r="AB339" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="340" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:28" ht="18" customHeight="1">
       <c r="A340" s="1">
         <v>46361</v>
       </c>
-      <c r="B340" s="2" t="s">
+      <c r="B340" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C340" s="2" t="s">
@@ -45826,15 +45844,15 @@
       <c r="AA340" s="2" t="s">
         <v>5011</v>
       </c>
-      <c r="AB340" s="9" t="s">
+      <c r="AB340" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="341" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:28" ht="18" customHeight="1">
       <c r="A341" s="1">
         <v>46362</v>
       </c>
-      <c r="B341" s="2" t="s">
+      <c r="B341" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C341" s="2" t="s">
@@ -45912,15 +45930,15 @@
       <c r="AA341" s="2" t="s">
         <v>5025</v>
       </c>
-      <c r="AB341" s="9" t="s">
+      <c r="AB341" s="2" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="342" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:28" ht="18" customHeight="1">
       <c r="A342" s="1">
         <v>46363</v>
       </c>
-      <c r="B342" s="2" t="s">
+      <c r="B342" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C342" s="2" t="s">
@@ -45998,15 +46016,15 @@
       <c r="AA342" s="2" t="s">
         <v>5040</v>
       </c>
-      <c r="AB342" s="9" t="s">
+      <c r="AB342" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="343" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:28" ht="18" customHeight="1">
       <c r="A343" s="1">
         <v>46364</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="B343" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C343" s="2" t="s">
@@ -46084,15 +46102,15 @@
       <c r="AA343" s="2" t="s">
         <v>5054</v>
       </c>
-      <c r="AB343" s="9" t="s">
+      <c r="AB343" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="344" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:28" ht="18" customHeight="1">
       <c r="A344" s="1">
         <v>46365</v>
       </c>
-      <c r="B344" s="2" t="s">
+      <c r="B344" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C344" s="2" t="s">
@@ -46170,15 +46188,15 @@
       <c r="AA344" s="2" t="s">
         <v>5068</v>
       </c>
-      <c r="AB344" s="9" t="s">
+      <c r="AB344" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="345" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:28" ht="18" customHeight="1">
       <c r="A345" s="1">
         <v>46366</v>
       </c>
-      <c r="B345" s="2" t="s">
+      <c r="B345" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C345" s="2" t="s">
@@ -46256,15 +46274,15 @@
       <c r="AA345" s="2" t="s">
         <v>5082</v>
       </c>
-      <c r="AB345" s="9" t="s">
+      <c r="AB345" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="346" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:28" ht="18" customHeight="1">
       <c r="A346" s="1">
         <v>46367</v>
       </c>
-      <c r="B346" s="2" t="s">
+      <c r="B346" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C346" s="2" t="s">
@@ -46342,15 +46360,15 @@
       <c r="AA346" s="2" t="s">
         <v>5096</v>
       </c>
-      <c r="AB346" s="9" t="s">
+      <c r="AB346" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="347" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:28" ht="18" customHeight="1">
       <c r="A347" s="1">
         <v>46368</v>
       </c>
-      <c r="B347" s="2" t="s">
+      <c r="B347" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C347" s="2" t="s">
@@ -46428,15 +46446,15 @@
       <c r="AA347" s="2" t="s">
         <v>5111</v>
       </c>
-      <c r="AB347" s="9" t="s">
+      <c r="AB347" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="348" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:28" ht="18" customHeight="1">
       <c r="A348" s="1">
         <v>46369</v>
       </c>
-      <c r="B348" s="2" t="s">
+      <c r="B348" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C348" s="2" t="s">
@@ -46514,15 +46532,15 @@
       <c r="AA348" s="2" t="s">
         <v>5124</v>
       </c>
-      <c r="AB348" s="9" t="s">
+      <c r="AB348" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="349" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:28" ht="18" customHeight="1">
       <c r="A349" s="1">
         <v>46370</v>
       </c>
-      <c r="B349" s="2" t="s">
+      <c r="B349" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C349" s="2" t="s">
@@ -46600,15 +46618,15 @@
       <c r="AA349" s="2" t="s">
         <v>5140</v>
       </c>
-      <c r="AB349" s="9" t="s">
+      <c r="AB349" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="350" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:28" ht="18" customHeight="1">
       <c r="A350" s="1">
         <v>46371</v>
       </c>
-      <c r="B350" s="2" t="s">
+      <c r="B350" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C350" s="2" t="s">
@@ -46686,15 +46704,15 @@
       <c r="AA350" s="2" t="s">
         <v>5154</v>
       </c>
-      <c r="AB350" s="9" t="s">
+      <c r="AB350" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="351" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:28" ht="18" customHeight="1">
       <c r="A351" s="1">
         <v>46372</v>
       </c>
-      <c r="B351" s="2" t="s">
+      <c r="B351" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C351" s="2" t="s">
@@ -46772,15 +46790,15 @@
       <c r="AA351" s="2" t="s">
         <v>5169</v>
       </c>
-      <c r="AB351" s="9" t="s">
+      <c r="AB351" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="352" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:28" ht="18" customHeight="1">
       <c r="A352" s="1">
         <v>46373</v>
       </c>
-      <c r="B352" s="2" t="s">
+      <c r="B352" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C352" s="2" t="s">
@@ -46858,15 +46876,15 @@
       <c r="AA352" s="2" t="s">
         <v>5183</v>
       </c>
-      <c r="AB352" s="9" t="s">
+      <c r="AB352" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="353" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:28" ht="18" customHeight="1">
       <c r="A353" s="1">
         <v>46374</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B353" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C353" s="2" t="s">
@@ -46944,15 +46962,15 @@
       <c r="AA353" s="2" t="s">
         <v>5197</v>
       </c>
-      <c r="AB353" s="9" t="s">
+      <c r="AB353" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="354" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:28" ht="18" customHeight="1">
       <c r="A354" s="1">
         <v>46375</v>
       </c>
-      <c r="B354" s="2" t="s">
+      <c r="B354" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C354" s="2" t="s">
@@ -47030,15 +47048,15 @@
       <c r="AA354" s="2" t="s">
         <v>5212</v>
       </c>
-      <c r="AB354" s="9" t="s">
+      <c r="AB354" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="355" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:28" ht="18" customHeight="1">
       <c r="A355" s="1">
         <v>46376</v>
       </c>
-      <c r="B355" s="2" t="s">
+      <c r="B355" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C355" s="2" t="s">
@@ -47116,15 +47134,15 @@
       <c r="AA355" s="2" t="s">
         <v>5226</v>
       </c>
-      <c r="AB355" s="9" t="s">
+      <c r="AB355" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="356" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:28" ht="18" customHeight="1">
       <c r="A356" s="1">
         <v>46377</v>
       </c>
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C356" s="2" t="s">
@@ -47202,15 +47220,15 @@
       <c r="AA356" s="2" t="s">
         <v>5241</v>
       </c>
-      <c r="AB356" s="9" t="s">
+      <c r="AB356" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="357" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:28" ht="18" customHeight="1">
       <c r="A357" s="1">
         <v>46378</v>
       </c>
-      <c r="B357" s="2" t="s">
+      <c r="B357" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C357" s="2" t="s">
@@ -47288,15 +47306,15 @@
       <c r="AA357" s="2" t="s">
         <v>5255</v>
       </c>
-      <c r="AB357" s="9" t="s">
+      <c r="AB357" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="358" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:28" ht="18" customHeight="1">
       <c r="A358" s="1">
         <v>46379</v>
       </c>
-      <c r="B358" s="2" t="s">
+      <c r="B358" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C358" s="2" t="s">
@@ -47374,15 +47392,15 @@
       <c r="AA358" s="2" t="s">
         <v>5270</v>
       </c>
-      <c r="AB358" s="9" t="s">
+      <c r="AB358" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="359" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:28" ht="18" customHeight="1">
       <c r="A359" s="1">
         <v>46380</v>
       </c>
-      <c r="B359" s="2" t="s">
+      <c r="B359" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C359" s="2" t="s">
@@ -47460,15 +47478,15 @@
       <c r="AA359" s="2" t="s">
         <v>5285</v>
       </c>
-      <c r="AB359" s="9" t="s">
+      <c r="AB359" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="360" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:28" ht="18" customHeight="1">
       <c r="A360" s="1">
         <v>46381</v>
       </c>
-      <c r="B360" s="2" t="s">
+      <c r="B360" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C360" s="2" t="s">
@@ -47546,15 +47564,15 @@
       <c r="AA360" s="2" t="s">
         <v>5300</v>
       </c>
-      <c r="AB360" s="9" t="s">
+      <c r="AB360" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="361" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:28" ht="18" customHeight="1">
       <c r="A361" s="1">
         <v>46382</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B361" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C361" s="2" t="s">
@@ -47632,15 +47650,15 @@
       <c r="AA361" s="2" t="s">
         <v>5315</v>
       </c>
-      <c r="AB361" s="9" t="s">
+      <c r="AB361" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="362" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:28" ht="18" customHeight="1">
       <c r="A362" s="1">
         <v>46383</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="B362" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C362" s="2" t="s">
@@ -47718,15 +47736,15 @@
       <c r="AA362" s="2" t="s">
         <v>5329</v>
       </c>
-      <c r="AB362" s="9" t="s">
+      <c r="AB362" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="363" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:28" ht="18" customHeight="1">
       <c r="A363" s="1">
         <v>46384</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="B363" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C363" s="2" t="s">
@@ -47804,15 +47822,15 @@
       <c r="AA363" s="2" t="s">
         <v>5343</v>
       </c>
-      <c r="AB363" s="9" t="s">
+      <c r="AB363" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="364" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:28" ht="18" customHeight="1">
       <c r="A364" s="1">
         <v>46385</v>
       </c>
-      <c r="B364" s="2" t="s">
+      <c r="B364" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C364" s="2" t="s">
@@ -47890,15 +47908,15 @@
       <c r="AA364" s="2" t="s">
         <v>5359</v>
       </c>
-      <c r="AB364" s="9" t="s">
+      <c r="AB364" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="365" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:28" ht="18" customHeight="1">
       <c r="A365" s="1">
         <v>46386</v>
       </c>
-      <c r="B365" s="2" t="s">
+      <c r="B365" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C365" s="2" t="s">
@@ -47976,15 +47994,15 @@
       <c r="AA365" s="2" t="s">
         <v>5373</v>
       </c>
-      <c r="AB365" s="9" t="s">
+      <c r="AB365" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
-    <row r="366" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:28" ht="18" customHeight="1">
       <c r="A366" s="1">
         <v>46387</v>
       </c>
-      <c r="B366" s="2" t="s">
+      <c r="B366" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C366" s="2" t="s">
@@ -48062,7 +48080,7 @@
       <c r="AA366" s="2" t="s">
         <v>5387</v>
       </c>
-      <c r="AB366" s="9" t="s">
+      <c r="AB366" s="2" t="s">
         <v>5125</v>
       </c>
     </row>
